--- a/research/traditional_assets/database/data/sweden/sweden_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_real_estate_general_diversified.xlsx
@@ -1249,7 +1249,7 @@
         <v>1.0952380952381</v>
       </c>
       <c r="F2">
-        <v>4.50082811334834</v>
+        <v>4.50082811334833</v>
       </c>
       <c r="G2">
         <v>21.5539568345324</v>
@@ -1267,7 +1267,7 @@
         <v>173.1</v>
       </c>
       <c r="L2">
-        <v>490.704152174667</v>
+        <v>490.704152174666</v>
       </c>
       <c r="M2">
         <v>748.4</v>
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1531,22 +1531,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0686193600957969</v>
+        <v>0.06851373421399956</v>
       </c>
       <c r="C2">
-        <v>640.5398917753603</v>
+        <v>635.0669420350138</v>
       </c>
       <c r="D2">
-        <v>616.6398917753603</v>
+        <v>618.8899420350137</v>
       </c>
       <c r="E2">
-        <v>-599.2</v>
+        <v>-591.4770000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.723000000000001</v>
       </c>
       <c r="G2">
         <v>23.9</v>
@@ -1567,28 +1567,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3884669</v>
       </c>
       <c r="N2">
-        <v>46.13333333333334</v>
+        <v>45.74486643333334</v>
       </c>
       <c r="O2">
-        <v>9.503466666666668</v>
+        <v>9.423442485266669</v>
       </c>
       <c r="P2">
-        <v>36.62986666666667</v>
+        <v>36.32142394806667</v>
       </c>
       <c r="Q2">
-        <v>36.82986666666667</v>
+        <v>36.52142394806667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0686193600957969</v>
+        <v>0.06880237597373692</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5312327014719846</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>118.7574368197994</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06851373421399956</v>
+        <v>0.06840810833220222</v>
       </c>
       <c r="C3">
-        <v>635.0669420350138</v>
+        <v>629.6104727955767</v>
       </c>
       <c r="D3">
-        <v>618.8899420350137</v>
+        <v>621.1564727955767</v>
       </c>
       <c r="E3">
-        <v>-591.4770000000001</v>
+        <v>-583.754</v>
       </c>
       <c r="F3">
-        <v>7.723000000000001</v>
+        <v>15.446</v>
       </c>
       <c r="G3">
         <v>23.9</v>
@@ -1649,28 +1649,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M3">
-        <v>0.3884669</v>
+        <v>0.7769338</v>
       </c>
       <c r="N3">
-        <v>45.74486643333334</v>
+        <v>45.35639953333334</v>
       </c>
       <c r="O3">
-        <v>9.423442485266669</v>
+        <v>9.343418303866668</v>
       </c>
       <c r="P3">
-        <v>36.32142394806667</v>
+        <v>36.01298122946667</v>
       </c>
       <c r="Q3">
-        <v>36.52142394806667</v>
+        <v>36.21298122946666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06880237597373692</v>
+        <v>0.0689891268695941</v>
       </c>
       <c r="T3">
-        <v>0.5312327014719846</v>
+        <v>0.5355456551869309</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.7574368197994</v>
+        <v>59.3787184098997</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1695,22 +1695,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06840810833220222</v>
+        <v>0.06830248245040488</v>
       </c>
       <c r="C4">
-        <v>629.6104727955767</v>
+        <v>624.1706657898294</v>
       </c>
       <c r="D4">
-        <v>621.1564727955767</v>
+        <v>623.4396657898294</v>
       </c>
       <c r="E4">
-        <v>-583.754</v>
+        <v>-576.0310000000001</v>
       </c>
       <c r="F4">
-        <v>15.446</v>
+        <v>23.169</v>
       </c>
       <c r="G4">
         <v>23.9</v>
@@ -1731,28 +1731,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M4">
-        <v>0.7769338</v>
+        <v>1.1654007</v>
       </c>
       <c r="N4">
-        <v>45.35639953333334</v>
+        <v>44.96793263333334</v>
       </c>
       <c r="O4">
-        <v>9.343418303866668</v>
+        <v>9.26339412246667</v>
       </c>
       <c r="P4">
-        <v>36.01298122946667</v>
+        <v>35.70453851086667</v>
       </c>
       <c r="Q4">
-        <v>36.21298122946666</v>
+        <v>35.90453851086667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0689891268695941</v>
+        <v>0.06917972829938647</v>
       </c>
       <c r="T4">
-        <v>0.5355456551869309</v>
+        <v>0.5399475357825976</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.3787184098997</v>
+        <v>39.58581227326648</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1777,22 +1777,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06830248245040488</v>
+        <v>0.06819685656860754</v>
       </c>
       <c r="C5">
-        <v>624.1706657898294</v>
+        <v>618.7477054323997</v>
       </c>
       <c r="D5">
-        <v>623.4396657898294</v>
+        <v>625.7397054323998</v>
       </c>
       <c r="E5">
-        <v>-576.0310000000001</v>
+        <v>-568.308</v>
       </c>
       <c r="F5">
-        <v>23.169</v>
+        <v>30.892</v>
       </c>
       <c r="G5">
         <v>23.9</v>
@@ -1813,28 +1813,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M5">
-        <v>1.1654007</v>
+        <v>1.5538676</v>
       </c>
       <c r="N5">
-        <v>44.96793263333334</v>
+        <v>44.57946573333334</v>
       </c>
       <c r="O5">
-        <v>9.26339412246667</v>
+        <v>9.183369941066669</v>
       </c>
       <c r="P5">
-        <v>35.70453851086667</v>
+        <v>35.39609579226668</v>
       </c>
       <c r="Q5">
-        <v>35.90453851086667</v>
+        <v>35.59609579226668</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06917972829938647</v>
+        <v>0.06937430059229951</v>
       </c>
       <c r="T5">
-        <v>0.5399475357825976</v>
+        <v>0.5444411222240074</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.58581227326648</v>
+        <v>29.68935920494986</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1859,22 +1859,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06819685656860754</v>
+        <v>0.06809123068681019</v>
       </c>
       <c r="C6">
-        <v>618.7477054323997</v>
+        <v>613.3417788694171</v>
       </c>
       <c r="D6">
-        <v>625.7397054323998</v>
+        <v>628.0567788694171</v>
       </c>
       <c r="E6">
-        <v>-568.308</v>
+        <v>-560.585</v>
       </c>
       <c r="F6">
-        <v>30.892</v>
+        <v>38.61500000000001</v>
       </c>
       <c r="G6">
         <v>23.9</v>
@@ -1895,28 +1895,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M6">
-        <v>1.5538676</v>
+        <v>1.9423345</v>
       </c>
       <c r="N6">
-        <v>44.57946573333334</v>
+        <v>44.19099883333334</v>
       </c>
       <c r="O6">
-        <v>9.183369941066669</v>
+        <v>9.103345759666668</v>
       </c>
       <c r="P6">
-        <v>35.39609579226668</v>
+        <v>35.08765307366667</v>
       </c>
       <c r="Q6">
-        <v>35.59609579226668</v>
+        <v>35.28765307366668</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06937430059229951</v>
+        <v>0.06957296914401073</v>
       </c>
       <c r="T6">
-        <v>0.5444411222240074</v>
+        <v>0.5490293104852364</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.68935920494986</v>
+        <v>23.75148736395988</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06809123068681019</v>
+        <v>0.06798560480501284</v>
       </c>
       <c r="C7">
-        <v>613.3417788694171</v>
+        <v>607.953076029274</v>
       </c>
       <c r="D7">
-        <v>628.0567788694171</v>
+        <v>630.391076029274</v>
       </c>
       <c r="E7">
-        <v>-560.585</v>
+        <v>-552.8620000000001</v>
       </c>
       <c r="F7">
-        <v>38.61500000000001</v>
+        <v>46.33800000000001</v>
       </c>
       <c r="G7">
         <v>23.9</v>
@@ -1977,28 +1977,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M7">
-        <v>1.9423345</v>
+        <v>2.3308014</v>
       </c>
       <c r="N7">
-        <v>44.19099883333334</v>
+        <v>43.80253193333334</v>
       </c>
       <c r="O7">
-        <v>9.103345759666668</v>
+        <v>9.023321578266669</v>
       </c>
       <c r="P7">
-        <v>35.08765307366667</v>
+        <v>34.77921035506667</v>
       </c>
       <c r="Q7">
-        <v>35.28765307366668</v>
+        <v>34.97921035506667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06957296914401073</v>
+        <v>0.06977586468618388</v>
       </c>
       <c r="T7">
-        <v>0.5490293104852364</v>
+        <v>0.5537151197733</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.75148736395988</v>
+        <v>19.79290613663323</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2023,22 +2023,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06798560480501284</v>
+        <v>0.06787997892321551</v>
       </c>
       <c r="C8">
-        <v>607.953076029274</v>
+        <v>602.5817896745203</v>
       </c>
       <c r="D8">
-        <v>630.391076029274</v>
+        <v>632.7427896745204</v>
       </c>
       <c r="E8">
-        <v>-552.8620000000001</v>
+        <v>-545.139</v>
       </c>
       <c r="F8">
-        <v>46.338</v>
+        <v>54.061</v>
       </c>
       <c r="G8">
         <v>23.9</v>
@@ -2059,28 +2059,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M8">
-        <v>2.3308014</v>
+        <v>2.7192683</v>
       </c>
       <c r="N8">
-        <v>43.80253193333334</v>
+        <v>43.41406503333334</v>
       </c>
       <c r="O8">
-        <v>9.023321578266669</v>
+        <v>8.943297396866669</v>
       </c>
       <c r="P8">
-        <v>34.77921035506667</v>
+        <v>34.47076763646667</v>
       </c>
       <c r="Q8">
-        <v>34.97921035506667</v>
+        <v>34.67076763646666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06977586468618388</v>
+        <v>0.06998312357335001</v>
       </c>
       <c r="T8">
-        <v>0.5537151197733</v>
+        <v>0.5585016991535801</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.79290613663324</v>
+        <v>16.9653481171142</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06787997892321551</v>
+        <v>0.06777435304141817</v>
       </c>
       <c r="C9">
-        <v>602.5817896745203</v>
+        <v>597.2281154549308</v>
       </c>
       <c r="D9">
-        <v>632.7427896745204</v>
+        <v>635.1121154549309</v>
       </c>
       <c r="E9">
-        <v>-545.139</v>
+        <v>-537.4160000000001</v>
       </c>
       <c r="F9">
-        <v>54.06100000000001</v>
+        <v>61.78400000000001</v>
       </c>
       <c r="G9">
         <v>23.9</v>
@@ -2141,28 +2141,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M9">
-        <v>2.7192683</v>
+        <v>3.1077352</v>
       </c>
       <c r="N9">
-        <v>43.41406503333334</v>
+        <v>43.02559813333334</v>
       </c>
       <c r="O9">
-        <v>8.943297396866669</v>
+        <v>8.863273215466668</v>
       </c>
       <c r="P9">
-        <v>34.47076763646667</v>
+        <v>34.16232491786667</v>
       </c>
       <c r="Q9">
-        <v>34.67076763646666</v>
+        <v>34.36232491786667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06998312357335001</v>
+        <v>0.07019488808849801</v>
       </c>
       <c r="T9">
-        <v>0.5585016991535801</v>
+        <v>0.5633923346073445</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.9653481171142</v>
+        <v>14.84467960247493</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06777435304141817</v>
+        <v>0.06766872715962084</v>
       </c>
       <c r="C10">
-        <v>597.2281154549308</v>
+        <v>591.8922519617604</v>
       </c>
       <c r="D10">
-        <v>635.1121154549309</v>
+        <v>637.4992519617604</v>
       </c>
       <c r="E10">
-        <v>-537.4160000000001</v>
+        <v>-529.693</v>
       </c>
       <c r="F10">
-        <v>61.78400000000001</v>
+        <v>69.50700000000001</v>
       </c>
       <c r="G10">
         <v>23.9</v>
@@ -2223,28 +2223,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M10">
-        <v>3.1077352</v>
+        <v>3.4962021</v>
       </c>
       <c r="N10">
-        <v>43.02559813333334</v>
+        <v>42.63713123333334</v>
       </c>
       <c r="O10">
-        <v>8.863273215466668</v>
+        <v>8.783249034066669</v>
       </c>
       <c r="P10">
-        <v>34.16232491786667</v>
+        <v>33.85388219926667</v>
       </c>
       <c r="Q10">
-        <v>34.36232491786667</v>
+        <v>34.05388219926667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07019488808849801</v>
+        <v>0.0704113067688141</v>
       </c>
       <c r="T10">
-        <v>0.5633923346073445</v>
+        <v>0.5683904565545982</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.84467960247493</v>
+        <v>13.19527075775549</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2269,22 +2269,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06766872715962084</v>
+        <v>0.06768220127782348</v>
       </c>
       <c r="C11">
-        <v>591.8922519617604</v>
+        <v>583.863739898748</v>
       </c>
       <c r="D11">
-        <v>637.4992519617604</v>
+        <v>637.193739898748</v>
       </c>
       <c r="E11">
-        <v>-529.693</v>
+        <v>-521.97</v>
       </c>
       <c r="F11">
-        <v>69.50700000000001</v>
+        <v>77.23</v>
       </c>
       <c r="G11">
         <v>23.9</v>
@@ -2305,45 +2305,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M11">
-        <v>3.4962021</v>
+        <v>4.000514</v>
       </c>
       <c r="N11">
-        <v>42.63713123333334</v>
+        <v>42.13281933333334</v>
       </c>
       <c r="O11">
-        <v>8.783249034066669</v>
+        <v>8.679360782666668</v>
       </c>
       <c r="P11">
-        <v>33.85388219926667</v>
+        <v>33.45345855066667</v>
       </c>
       <c r="Q11">
-        <v>34.05388219926667</v>
+        <v>33.65345855066667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0704113067688141</v>
+        <v>0.0706325347531372</v>
       </c>
       <c r="T11">
-        <v>0.5683904565545982</v>
+        <v>0.5734996478784575</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.206</v>
       </c>
       <c r="W11">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.19527075775549</v>
+        <v>11.53185149041682</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06768220127782348</v>
+        <v>0.06758848539602615</v>
       </c>
       <c r="C12">
-        <v>583.863739898748</v>
+        <v>578.2717378667523</v>
       </c>
       <c r="D12">
-        <v>637.193739898748</v>
+        <v>639.3247378667523</v>
       </c>
       <c r="E12">
-        <v>-521.97</v>
+        <v>-514.2470000000001</v>
       </c>
       <c r="F12">
-        <v>77.23000000000002</v>
+        <v>84.953</v>
       </c>
       <c r="G12">
         <v>23.9</v>
@@ -2387,28 +2387,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M12">
-        <v>4.000514000000001</v>
+        <v>4.4005654</v>
       </c>
       <c r="N12">
-        <v>42.13281933333334</v>
+        <v>41.73276793333334</v>
       </c>
       <c r="O12">
-        <v>8.679360782666668</v>
+        <v>8.59695019426667</v>
       </c>
       <c r="P12">
-        <v>33.45345855066667</v>
+        <v>33.13581773906667</v>
       </c>
       <c r="Q12">
-        <v>33.65345855066667</v>
+        <v>33.33581773906667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0706325347531372</v>
+        <v>0.07085873415283837</v>
       </c>
       <c r="T12">
-        <v>0.5734996478784575</v>
+        <v>0.5787236524904936</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.53185149041681</v>
+        <v>10.48350135492438</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06758848539602615</v>
+        <v>0.0676567455142288</v>
       </c>
       <c r="C13">
-        <v>578.2717378667523</v>
+        <v>568.9951698976596</v>
       </c>
       <c r="D13">
-        <v>639.3247378667523</v>
+        <v>637.7711698976597</v>
       </c>
       <c r="E13">
-        <v>-514.2470000000001</v>
+        <v>-506.5240000000001</v>
       </c>
       <c r="F13">
-        <v>84.953</v>
+        <v>92.676</v>
       </c>
       <c r="G13">
         <v>23.9</v>
@@ -2469,45 +2469,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M13">
-        <v>4.4005654</v>
+        <v>4.958166</v>
       </c>
       <c r="N13">
-        <v>41.73276793333334</v>
+        <v>41.17516733333334</v>
       </c>
       <c r="O13">
-        <v>8.59695019426667</v>
+        <v>8.482084470666669</v>
       </c>
       <c r="P13">
-        <v>33.13581773906667</v>
+        <v>32.69308286266667</v>
       </c>
       <c r="Q13">
-        <v>33.33581773906667</v>
+        <v>32.89308286266667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07085873415283837</v>
+        <v>0.07109007444798728</v>
       </c>
       <c r="T13">
-        <v>0.5787236524904936</v>
+        <v>0.5840663844800759</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.206</v>
       </c>
       <c r="W13">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.48350135492438</v>
+        <v>9.304515688529456</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0676567455142288</v>
+        <v>0.06757652763243147</v>
       </c>
       <c r="C14">
-        <v>568.9951698976596</v>
+        <v>563.0986703179386</v>
       </c>
       <c r="D14">
-        <v>637.7711698976597</v>
+        <v>639.5976703179387</v>
       </c>
       <c r="E14">
-        <v>-506.5240000000001</v>
+        <v>-498.801</v>
       </c>
       <c r="F14">
-        <v>92.676</v>
+        <v>100.399</v>
       </c>
       <c r="G14">
         <v>23.9</v>
@@ -2551,28 +2551,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M14">
-        <v>4.958166</v>
+        <v>5.3713465</v>
       </c>
       <c r="N14">
-        <v>41.17516733333334</v>
+        <v>40.76198683333334</v>
       </c>
       <c r="O14">
-        <v>8.482084470666669</v>
+        <v>8.396969287666668</v>
       </c>
       <c r="P14">
-        <v>32.69308286266667</v>
+        <v>32.36501754566667</v>
       </c>
       <c r="Q14">
-        <v>32.89308286266667</v>
+        <v>32.56501754566668</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07109007444798728</v>
+        <v>0.07132673291084077</v>
       </c>
       <c r="T14">
-        <v>0.5840663844800759</v>
+        <v>0.5895319378947059</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.304515688529456</v>
+        <v>8.588783712488727</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2597,22 +2597,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06757652763243147</v>
+        <v>0.06749630975063411</v>
       </c>
       <c r="C15">
-        <v>563.0986703179386</v>
+        <v>557.2126625433873</v>
       </c>
       <c r="D15">
-        <v>639.5976703179387</v>
+        <v>641.4346625433873</v>
       </c>
       <c r="E15">
-        <v>-498.801</v>
+        <v>-491.078</v>
       </c>
       <c r="F15">
-        <v>100.399</v>
+        <v>108.122</v>
       </c>
       <c r="G15">
         <v>23.9</v>
@@ -2633,28 +2633,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M15">
-        <v>5.3713465</v>
+        <v>5.784527000000001</v>
       </c>
       <c r="N15">
-        <v>40.76198683333334</v>
+        <v>40.34880633333334</v>
       </c>
       <c r="O15">
-        <v>8.396969287666668</v>
+        <v>8.311854104666669</v>
       </c>
       <c r="P15">
-        <v>32.36501754566667</v>
+        <v>32.03695222866668</v>
       </c>
       <c r="Q15">
-        <v>32.56501754566668</v>
+        <v>32.23695222866668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07132673291084077</v>
+        <v>0.07156889505887688</v>
       </c>
       <c r="T15">
-        <v>0.5895319378947059</v>
+        <v>0.5951245972026995</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.588783712488727</v>
+        <v>7.975299161596676</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06749630975063411</v>
+        <v>0.06751137186883678</v>
       </c>
       <c r="C16">
-        <v>557.2126625433873</v>
+        <v>549.1439353122937</v>
       </c>
       <c r="D16">
-        <v>641.4346625433873</v>
+        <v>641.0889353122938</v>
       </c>
       <c r="E16">
-        <v>-491.078</v>
+        <v>-483.355</v>
       </c>
       <c r="F16">
-        <v>108.122</v>
+        <v>115.845</v>
       </c>
       <c r="G16">
         <v>23.9</v>
@@ -2715,45 +2715,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M16">
-        <v>5.784527000000001</v>
+        <v>6.290383500000002</v>
       </c>
       <c r="N16">
-        <v>40.34880633333334</v>
+        <v>39.84294983333334</v>
       </c>
       <c r="O16">
-        <v>8.311854104666669</v>
+        <v>8.207647665666668</v>
       </c>
       <c r="P16">
-        <v>32.03695222866668</v>
+        <v>31.63530216766667</v>
       </c>
       <c r="Q16">
-        <v>32.23695222866668</v>
+        <v>31.83530216766666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07156889505887688</v>
+        <v>0.07181675513980798</v>
       </c>
       <c r="T16">
-        <v>0.5951245972026995</v>
+        <v>0.6008488484944106</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.975299161596676</v>
+        <v>7.333946067570177</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06751137186883678</v>
+        <v>0.06743750598703943</v>
       </c>
       <c r="C17">
-        <v>549.1439353122937</v>
+        <v>543.1199876229452</v>
       </c>
       <c r="D17">
-        <v>641.0889353122938</v>
+        <v>642.7879876229453</v>
       </c>
       <c r="E17">
-        <v>-483.355</v>
+        <v>-475.6320000000001</v>
       </c>
       <c r="F17">
-        <v>115.845</v>
+        <v>123.568</v>
       </c>
       <c r="G17">
         <v>23.9</v>
@@ -2797,28 +2797,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M17">
-        <v>6.2903835</v>
+        <v>6.709742400000001</v>
       </c>
       <c r="N17">
-        <v>39.84294983333334</v>
+        <v>39.42359093333334</v>
       </c>
       <c r="O17">
-        <v>8.20764766566667</v>
+        <v>8.121259732266669</v>
       </c>
       <c r="P17">
-        <v>31.63530216766667</v>
+        <v>31.30233120106667</v>
       </c>
       <c r="Q17">
-        <v>31.83530216766667</v>
+        <v>31.50233120106667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07181675513980798</v>
+        <v>0.07207051665123743</v>
       </c>
       <c r="T17">
-        <v>0.6008488484944106</v>
+        <v>0.6067093914835434</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.33394606757018</v>
+        <v>6.875574438347042</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2843,22 +2843,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06743750598703943</v>
+        <v>0.0673636401052421</v>
       </c>
       <c r="C18">
-        <v>543.1199876229452</v>
+        <v>537.1050697253747</v>
       </c>
       <c r="D18">
-        <v>642.7879876229453</v>
+        <v>644.4960697253748</v>
       </c>
       <c r="E18">
-        <v>-475.6320000000001</v>
+        <v>-467.909</v>
       </c>
       <c r="F18">
-        <v>123.568</v>
+        <v>131.291</v>
       </c>
       <c r="G18">
         <v>23.9</v>
@@ -2879,28 +2879,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M18">
-        <v>6.709742400000001</v>
+        <v>7.129101300000001</v>
       </c>
       <c r="N18">
-        <v>39.42359093333334</v>
+        <v>39.00423203333334</v>
       </c>
       <c r="O18">
-        <v>8.121259732266669</v>
+        <v>8.034871798866668</v>
       </c>
       <c r="P18">
-        <v>31.30233120106667</v>
+        <v>30.96936023446667</v>
       </c>
       <c r="Q18">
-        <v>31.50233120106667</v>
+        <v>31.16936023446667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07207051665123743</v>
+        <v>0.07233039289788204</v>
       </c>
       <c r="T18">
-        <v>0.6067093914835434</v>
+        <v>0.6127111523760288</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.875574438347042</v>
+        <v>6.471128883150157</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2925,22 +2925,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0673636401052421</v>
+        <v>0.06728977422344476</v>
       </c>
       <c r="C19">
-        <v>537.1050697253747</v>
+        <v>531.0992537960411</v>
       </c>
       <c r="D19">
-        <v>644.4960697253748</v>
+        <v>646.2132537960412</v>
       </c>
       <c r="E19">
-        <v>-467.909</v>
+        <v>-460.186</v>
       </c>
       <c r="F19">
-        <v>131.291</v>
+        <v>139.014</v>
       </c>
       <c r="G19">
         <v>23.9</v>
@@ -2961,28 +2961,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M19">
-        <v>7.129101300000001</v>
+        <v>7.548460200000002</v>
       </c>
       <c r="N19">
-        <v>39.00423203333334</v>
+        <v>38.58487313333334</v>
       </c>
       <c r="O19">
-        <v>8.034871798866668</v>
+        <v>7.948483865466669</v>
       </c>
       <c r="P19">
-        <v>30.96936023446667</v>
+        <v>30.63638926786667</v>
       </c>
       <c r="Q19">
-        <v>31.16936023446667</v>
+        <v>30.83638926786667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07233039289788204</v>
+        <v>0.07259660758956678</v>
       </c>
       <c r="T19">
-        <v>0.6127111523760288</v>
+        <v>0.6188592976805261</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.471128883150157</v>
+        <v>6.111621722975148</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3007,22 +3007,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06728977422344476</v>
+        <v>0.0673667683416474</v>
       </c>
       <c r="C20">
-        <v>531.0992537960411</v>
+        <v>521.5865480095301</v>
       </c>
       <c r="D20">
-        <v>646.2132537960412</v>
+        <v>644.4235480095301</v>
       </c>
       <c r="E20">
-        <v>-460.186</v>
+        <v>-452.463</v>
       </c>
       <c r="F20">
-        <v>139.014</v>
+        <v>146.737</v>
       </c>
       <c r="G20">
         <v>23.9</v>
@@ -3043,45 +3043,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M20">
-        <v>7.548460200000001</v>
+        <v>8.114556100000001</v>
       </c>
       <c r="N20">
-        <v>38.58487313333334</v>
+        <v>38.01877723333334</v>
       </c>
       <c r="O20">
-        <v>7.948483865466669</v>
+        <v>7.831868110066669</v>
       </c>
       <c r="P20">
-        <v>30.63638926786667</v>
+        <v>30.18690912326667</v>
       </c>
       <c r="Q20">
-        <v>30.83638926786667</v>
+        <v>30.38690912326667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07259660758956678</v>
+        <v>0.07286939548351531</v>
       </c>
       <c r="T20">
-        <v>0.6188592976805261</v>
+        <v>0.6251592490419244</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.206</v>
       </c>
       <c r="W20">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.111621722975149</v>
+        <v>5.685256564229475</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3089,22 +3089,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0673667683416474</v>
+        <v>0.06730084245985007</v>
       </c>
       <c r="C21">
-        <v>521.5865480095301</v>
+        <v>515.3953643157762</v>
       </c>
       <c r="D21">
-        <v>644.4235480095301</v>
+        <v>645.9553643157763</v>
       </c>
       <c r="E21">
-        <v>-452.463</v>
+        <v>-444.74</v>
       </c>
       <c r="F21">
-        <v>146.737</v>
+        <v>154.46</v>
       </c>
       <c r="G21">
         <v>23.9</v>
@@ -3125,28 +3125,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M21">
-        <v>8.114556100000001</v>
+        <v>8.541638000000003</v>
       </c>
       <c r="N21">
-        <v>38.01877723333334</v>
+        <v>37.59169533333333</v>
       </c>
       <c r="O21">
-        <v>7.831868110066669</v>
+        <v>7.743889238666667</v>
       </c>
       <c r="P21">
-        <v>30.18690912326667</v>
+        <v>29.84780609466667</v>
       </c>
       <c r="Q21">
-        <v>30.38690912326667</v>
+        <v>30.04780609466667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07286939548351531</v>
+        <v>0.07314900307481259</v>
       </c>
       <c r="T21">
-        <v>0.6251592490419244</v>
+        <v>0.6316166991873579</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.685256564229475</v>
+        <v>5.400993736018001</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3171,22 +3171,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06730084245985007</v>
+        <v>0.06723491657805272</v>
       </c>
       <c r="C22">
-        <v>515.3953643157762</v>
+        <v>509.2114803307619</v>
       </c>
       <c r="D22">
-        <v>645.9553643157763</v>
+        <v>647.4944803307619</v>
       </c>
       <c r="E22">
-        <v>-444.74</v>
+        <v>-437.0170000000001</v>
       </c>
       <c r="F22">
-        <v>154.46</v>
+        <v>162.183</v>
       </c>
       <c r="G22">
         <v>23.9</v>
@@ -3207,28 +3207,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M22">
-        <v>8.541638000000003</v>
+        <v>8.968719900000002</v>
       </c>
       <c r="N22">
-        <v>37.59169533333333</v>
+        <v>37.16461343333334</v>
       </c>
       <c r="O22">
-        <v>7.743889238666667</v>
+        <v>7.655910367266668</v>
       </c>
       <c r="P22">
-        <v>29.84780609466667</v>
+        <v>29.50870306606667</v>
       </c>
       <c r="Q22">
-        <v>30.04780609466667</v>
+        <v>29.70870306606667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07314900307481259</v>
+        <v>0.07343568933930725</v>
       </c>
       <c r="T22">
-        <v>0.6316166991873579</v>
+        <v>0.6382376290833085</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.400993736018001</v>
+        <v>5.143803558112382</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3253,22 +3253,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06723491657805272</v>
+        <v>0.06716899069625538</v>
       </c>
       <c r="C23">
-        <v>509.2114803307619</v>
+        <v>503.034948358096</v>
       </c>
       <c r="D23">
-        <v>647.4944803307619</v>
+        <v>649.040948358096</v>
       </c>
       <c r="E23">
-        <v>-437.0170000000001</v>
+        <v>-429.294</v>
       </c>
       <c r="F23">
-        <v>162.183</v>
+        <v>169.906</v>
       </c>
       <c r="G23">
         <v>23.9</v>
@@ -3289,28 +3289,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M23">
-        <v>8.968719900000002</v>
+        <v>9.395801800000001</v>
       </c>
       <c r="N23">
-        <v>37.16461343333334</v>
+        <v>36.73753153333334</v>
       </c>
       <c r="O23">
-        <v>7.655910367266668</v>
+        <v>7.567931495866668</v>
       </c>
       <c r="P23">
-        <v>29.50870306606667</v>
+        <v>29.16960003746667</v>
       </c>
       <c r="Q23">
-        <v>29.70870306606667</v>
+        <v>29.36960003746667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07343568933930725</v>
+        <v>0.07372972653366075</v>
       </c>
       <c r="T23">
-        <v>0.6382376290833085</v>
+        <v>0.6450283264124886</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.143803558112382</v>
+        <v>4.909994305470911</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3335,22 +3335,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06716899069625538</v>
+        <v>0.06710306481445805</v>
       </c>
       <c r="C24">
-        <v>503.034948358096</v>
+        <v>496.8658212022697</v>
       </c>
       <c r="D24">
-        <v>649.040948358096</v>
+        <v>650.5948212022697</v>
       </c>
       <c r="E24">
-        <v>-429.294</v>
+        <v>-421.571</v>
       </c>
       <c r="F24">
-        <v>169.906</v>
+        <v>177.629</v>
       </c>
       <c r="G24">
         <v>23.9</v>
@@ -3371,28 +3371,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M24">
-        <v>9.395801800000001</v>
+        <v>9.822883700000002</v>
       </c>
       <c r="N24">
-        <v>36.73753153333334</v>
+        <v>36.31044963333333</v>
       </c>
       <c r="O24">
-        <v>7.567931495866668</v>
+        <v>7.479952624466668</v>
       </c>
       <c r="P24">
-        <v>29.16960003746667</v>
+        <v>28.83049700886666</v>
       </c>
       <c r="Q24">
-        <v>29.36960003746667</v>
+        <v>29.03049700886666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07372972653366075</v>
+        <v>0.07403140105773773</v>
       </c>
       <c r="T24">
-        <v>0.6450283264124886</v>
+        <v>0.6519954054904786</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.909994305470911</v>
+        <v>4.696516292189566</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3417,22 +3417,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06710306481445805</v>
+        <v>0.06703713893266069</v>
       </c>
       <c r="C25">
-        <v>496.8658212022697</v>
+        <v>490.7041521746665</v>
       </c>
       <c r="D25">
-        <v>650.5948212022697</v>
+        <v>652.1561521746665</v>
       </c>
       <c r="E25">
-        <v>-421.571</v>
+        <v>-413.848</v>
       </c>
       <c r="F25">
-        <v>177.629</v>
+        <v>185.352</v>
       </c>
       <c r="G25">
         <v>23.9</v>
@@ -3453,28 +3453,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M25">
-        <v>9.822883700000002</v>
+        <v>10.2499656</v>
       </c>
       <c r="N25">
-        <v>36.31044963333333</v>
+        <v>35.88336773333334</v>
       </c>
       <c r="O25">
-        <v>7.479952624466668</v>
+        <v>7.391973753066668</v>
       </c>
       <c r="P25">
-        <v>28.83049700886666</v>
+        <v>28.49139398026667</v>
       </c>
       <c r="Q25">
-        <v>29.03049700886666</v>
+        <v>28.69139398026667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07403140105773773</v>
+        <v>0.07434101438507987</v>
       </c>
       <c r="T25">
-        <v>0.6519954054904786</v>
+        <v>0.6591458287547316</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.696516292189566</v>
+        <v>4.500828113348334</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3499,22 +3499,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06703713893266069</v>
+        <v>0.06746746305086336</v>
       </c>
       <c r="C26">
-        <v>490.7041521746665</v>
+        <v>472.9228351754105</v>
       </c>
       <c r="D26">
-        <v>652.1561521746665</v>
+        <v>642.0978351754105</v>
       </c>
       <c r="E26">
-        <v>-413.8480000000001</v>
+        <v>-406.125</v>
       </c>
       <c r="F26">
-        <v>185.352</v>
+        <v>193.075</v>
       </c>
       <c r="G26">
         <v>23.9</v>
@@ -3535,45 +3535,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M26">
-        <v>10.2499656</v>
+        <v>11.159735</v>
       </c>
       <c r="N26">
-        <v>35.88336773333334</v>
+        <v>34.97359833333334</v>
       </c>
       <c r="O26">
-        <v>7.391973753066668</v>
+        <v>7.204561256666669</v>
       </c>
       <c r="P26">
-        <v>28.49139398026667</v>
+        <v>27.76903707666667</v>
       </c>
       <c r="Q26">
-        <v>28.69139398026667</v>
+        <v>27.96903707666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07434101438507987</v>
+        <v>0.07465888406781782</v>
       </c>
       <c r="T26">
-        <v>0.6591458287547316</v>
+        <v>0.666486929972698</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.206</v>
       </c>
       <c r="W26">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.500828113348335</v>
+        <v>4.133909392412395</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3581,22 +3581,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06746746305086336</v>
+        <v>0.06814392716906603</v>
       </c>
       <c r="C27">
-        <v>472.9228351754105</v>
+        <v>450.0006558310321</v>
       </c>
       <c r="D27">
-        <v>642.0978351754105</v>
+        <v>626.8986558310321</v>
       </c>
       <c r="E27">
-        <v>-406.125</v>
+        <v>-398.402</v>
       </c>
       <c r="F27">
-        <v>193.075</v>
+        <v>200.798</v>
       </c>
       <c r="G27">
         <v>23.9</v>
@@ -3617,45 +3617,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M27">
-        <v>11.159735</v>
+        <v>12.3089174</v>
       </c>
       <c r="N27">
-        <v>34.97359833333334</v>
+        <v>33.82441593333334</v>
       </c>
       <c r="O27">
-        <v>7.204561256666669</v>
+        <v>6.967829682266669</v>
       </c>
       <c r="P27">
-        <v>27.76903707666667</v>
+        <v>26.85658625106667</v>
       </c>
       <c r="Q27">
-        <v>27.96903707666667</v>
+        <v>27.05658625106667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07465888406781782</v>
+        <v>0.0749853448230622</v>
       </c>
       <c r="T27">
-        <v>0.666486929972698</v>
+        <v>0.6740264393316905</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.206</v>
       </c>
       <c r="W27">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.133909392412395</v>
+        <v>3.747960266053401</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06814392716906603</v>
+        <v>0.06812564128726868</v>
       </c>
       <c r="C28">
-        <v>450.0006558310321</v>
+        <v>442.6790447651567</v>
       </c>
       <c r="D28">
-        <v>626.8986558310321</v>
+        <v>627.3000447651568</v>
       </c>
       <c r="E28">
-        <v>-398.402</v>
+        <v>-390.679</v>
       </c>
       <c r="F28">
-        <v>200.798</v>
+        <v>208.521</v>
       </c>
       <c r="G28">
         <v>23.9</v>
@@ -3699,28 +3699,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M28">
-        <v>12.3089174</v>
+        <v>12.7823373</v>
       </c>
       <c r="N28">
-        <v>33.82441593333334</v>
+        <v>33.35099603333334</v>
       </c>
       <c r="O28">
-        <v>6.967829682266669</v>
+        <v>6.870305182866669</v>
       </c>
       <c r="P28">
-        <v>26.85658625106667</v>
+        <v>26.48069085046667</v>
       </c>
       <c r="Q28">
-        <v>27.05658625106667</v>
+        <v>26.68069085046667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0749853448230622</v>
+        <v>0.07532074970858724</v>
       </c>
       <c r="T28">
-        <v>0.6740264393316905</v>
+        <v>0.6817725105909294</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.747960266053401</v>
+        <v>3.609146922866237</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06812564128726868</v>
+        <v>0.06872985140547133</v>
       </c>
       <c r="C29">
-        <v>442.6790447651567</v>
+        <v>421.9596399334608</v>
       </c>
       <c r="D29">
-        <v>627.3000447651568</v>
+        <v>614.3036399334609</v>
       </c>
       <c r="E29">
-        <v>-390.679</v>
+        <v>-382.956</v>
       </c>
       <c r="F29">
-        <v>208.521</v>
+        <v>216.244</v>
       </c>
       <c r="G29">
         <v>23.9</v>
@@ -3781,45 +3781,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M29">
-        <v>12.7823373</v>
+        <v>13.8612404</v>
       </c>
       <c r="N29">
-        <v>33.35099603333334</v>
+        <v>32.27209293333334</v>
       </c>
       <c r="O29">
-        <v>6.870305182866669</v>
+        <v>6.648051144266669</v>
       </c>
       <c r="P29">
-        <v>26.48069085046667</v>
+        <v>25.62404178906667</v>
       </c>
       <c r="Q29">
-        <v>26.68069085046667</v>
+        <v>25.82404178906667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07532074970858724</v>
+        <v>0.07566547139648797</v>
       </c>
       <c r="T29">
-        <v>0.6817725105909294</v>
+        <v>0.6897337504962581</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.206</v>
       </c>
       <c r="W29">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.609146922866237</v>
+        <v>3.328225469153059</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3827,22 +3827,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06872985140547133</v>
+        <v>0.06873379752367399</v>
       </c>
       <c r="C30">
-        <v>421.9596399334608</v>
+        <v>414.1535297316432</v>
       </c>
       <c r="D30">
-        <v>614.3036399334609</v>
+        <v>614.2205297316433</v>
       </c>
       <c r="E30">
-        <v>-382.956</v>
+        <v>-375.233</v>
       </c>
       <c r="F30">
-        <v>216.244</v>
+        <v>223.967</v>
       </c>
       <c r="G30">
         <v>23.9</v>
@@ -3863,28 +3863,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M30">
-        <v>13.8612404</v>
+        <v>14.3562847</v>
       </c>
       <c r="N30">
-        <v>32.27209293333334</v>
+        <v>31.77704863333334</v>
       </c>
       <c r="O30">
-        <v>6.648051144266669</v>
+        <v>6.546072018466668</v>
       </c>
       <c r="P30">
-        <v>25.62404178906667</v>
+        <v>25.23097661486667</v>
       </c>
       <c r="Q30">
-        <v>25.82404178906667</v>
+        <v>25.43097661486667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07566547139648797</v>
+        <v>0.07601990355447041</v>
       </c>
       <c r="T30">
-        <v>0.6897337504962581</v>
+        <v>0.6979192506806102</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.328225469153059</v>
+        <v>3.213459073665022</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3909,22 +3909,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06873379752367399</v>
+        <v>0.06873774364187665</v>
       </c>
       <c r="C31">
-        <v>414.1535297316433</v>
+        <v>406.3474420150295</v>
       </c>
       <c r="D31">
-        <v>614.2205297316433</v>
+        <v>614.1374420150295</v>
       </c>
       <c r="E31">
-        <v>-375.2330000000001</v>
+        <v>-367.51</v>
       </c>
       <c r="F31">
-        <v>223.967</v>
+        <v>231.69</v>
       </c>
       <c r="G31">
         <v>23.9</v>
@@ -3945,28 +3945,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M31">
-        <v>14.3562847</v>
+        <v>14.851329</v>
       </c>
       <c r="N31">
-        <v>31.77704863333334</v>
+        <v>31.28200433333334</v>
       </c>
       <c r="O31">
-        <v>6.546072018466668</v>
+        <v>6.444092892666669</v>
       </c>
       <c r="P31">
-        <v>25.23097661486667</v>
+        <v>24.83791144066667</v>
       </c>
       <c r="Q31">
-        <v>25.43097661486667</v>
+        <v>25.03791144066667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07601990355447041</v>
+        <v>0.07638446234553808</v>
       </c>
       <c r="T31">
-        <v>0.6979192506806102</v>
+        <v>0.7063386222988011</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.213459073665022</v>
+        <v>3.106343771209522</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3991,22 +3991,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06873774364187665</v>
+        <v>0.0687416897600793</v>
       </c>
       <c r="C32">
-        <v>406.3474420150295</v>
+        <v>398.541376774496</v>
       </c>
       <c r="D32">
-        <v>614.1374420150295</v>
+        <v>614.0543767744961</v>
       </c>
       <c r="E32">
-        <v>-367.51</v>
+        <v>-359.787</v>
       </c>
       <c r="F32">
-        <v>231.69</v>
+        <v>239.413</v>
       </c>
       <c r="G32">
         <v>23.9</v>
@@ -4027,28 +4027,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M32">
-        <v>14.851329</v>
+        <v>15.3463733</v>
       </c>
       <c r="N32">
-        <v>31.28200433333334</v>
+        <v>30.78696003333334</v>
       </c>
       <c r="O32">
-        <v>6.444092892666669</v>
+        <v>6.342113766866668</v>
       </c>
       <c r="P32">
-        <v>24.83791144066667</v>
+        <v>24.44484626646667</v>
       </c>
       <c r="Q32">
-        <v>25.03791144066667</v>
+        <v>24.64484626646667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07638446234553808</v>
+        <v>0.07675958805808596</v>
       </c>
       <c r="T32">
-        <v>0.7063386222988011</v>
+        <v>0.7150020336740408</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.106343771209522</v>
+        <v>3.006139133428569</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4073,22 +4073,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0687416897600793</v>
+        <v>0.07072745987828197</v>
       </c>
       <c r="C33">
-        <v>398.541376774496</v>
+        <v>351.6872372778628</v>
       </c>
       <c r="D33">
-        <v>614.0543767744961</v>
+        <v>574.9232372778629</v>
       </c>
       <c r="E33">
-        <v>-359.787</v>
+        <v>-352.064</v>
       </c>
       <c r="F33">
-        <v>239.413</v>
+        <v>247.136</v>
       </c>
       <c r="G33">
         <v>23.9</v>
@@ -4109,45 +4109,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M33">
-        <v>15.3463733</v>
+        <v>17.7690784</v>
       </c>
       <c r="N33">
-        <v>30.78696003333334</v>
+        <v>28.36425493333334</v>
       </c>
       <c r="O33">
-        <v>6.342113766866668</v>
+        <v>5.843036516266668</v>
       </c>
       <c r="P33">
-        <v>24.44484626646667</v>
+        <v>22.52121841706667</v>
       </c>
       <c r="Q33">
-        <v>24.64484626646667</v>
+        <v>22.72121841706667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07675958805808596</v>
+        <v>0.07714574687982642</v>
       </c>
       <c r="T33">
-        <v>0.7150020336740408</v>
+        <v>0.7239202512661994</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.206</v>
       </c>
       <c r="W33">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.006139133428569</v>
+        <v>2.596270458986401</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4155,22 +4155,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07072745987828197</v>
+        <v>0.07079333799648463</v>
       </c>
       <c r="C34">
-        <v>351.6872372778628</v>
+        <v>342.7513496611562</v>
       </c>
       <c r="D34">
-        <v>574.9232372778629</v>
+        <v>573.7103496611562</v>
       </c>
       <c r="E34">
-        <v>-352.064</v>
+        <v>-344.341</v>
       </c>
       <c r="F34">
-        <v>247.136</v>
+        <v>254.859</v>
       </c>
       <c r="G34">
         <v>23.9</v>
@@ -4191,28 +4191,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M34">
-        <v>17.7690784</v>
+        <v>18.32436210000001</v>
       </c>
       <c r="N34">
-        <v>28.36425493333334</v>
+        <v>27.80897123333333</v>
       </c>
       <c r="O34">
-        <v>5.843036516266668</v>
+        <v>5.728648074066667</v>
       </c>
       <c r="P34">
-        <v>22.52121841706667</v>
+        <v>22.08032315926667</v>
       </c>
       <c r="Q34">
-        <v>22.72121841706667</v>
+        <v>22.28032315926667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07714574687982642</v>
+        <v>0.07754343283057408</v>
       </c>
       <c r="T34">
-        <v>0.7239202512661994</v>
+        <v>0.7331046843088702</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.596270458986401</v>
+        <v>2.517595596592873</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4237,22 +4237,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07079333799648463</v>
+        <v>0.07191206011468729</v>
       </c>
       <c r="C35">
-        <v>342.7513496611562</v>
+        <v>315.1857832075103</v>
       </c>
       <c r="D35">
-        <v>573.7103496611562</v>
+        <v>553.8677832075103</v>
       </c>
       <c r="E35">
-        <v>-344.341</v>
+        <v>-336.618</v>
       </c>
       <c r="F35">
-        <v>254.859</v>
+        <v>262.5820000000001</v>
       </c>
       <c r="G35">
         <v>23.9</v>
@@ -4273,45 +4273,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M35">
-        <v>18.32436210000001</v>
+        <v>19.90371560000001</v>
       </c>
       <c r="N35">
-        <v>27.80897123333333</v>
+        <v>26.22961773333333</v>
       </c>
       <c r="O35">
-        <v>5.728648074066667</v>
+        <v>5.403301253066667</v>
       </c>
       <c r="P35">
-        <v>22.08032315926667</v>
+        <v>20.82631648026667</v>
       </c>
       <c r="Q35">
-        <v>22.28032315926667</v>
+        <v>21.02631648026667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07754343283057408</v>
+        <v>0.07795316987073832</v>
       </c>
       <c r="T35">
-        <v>0.7331046843088702</v>
+        <v>0.7425674335043493</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.206</v>
       </c>
       <c r="W35">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.517595596592873</v>
+        <v>2.317825187038611</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4319,22 +4319,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07191206011468729</v>
+        <v>0.07200890423288994</v>
       </c>
       <c r="C36">
-        <v>315.1857832075103</v>
+        <v>305.8094364820255</v>
       </c>
       <c r="D36">
-        <v>553.8677832075103</v>
+        <v>552.2144364820256</v>
       </c>
       <c r="E36">
-        <v>-336.618</v>
+        <v>-328.895</v>
       </c>
       <c r="F36">
-        <v>262.5820000000001</v>
+        <v>270.3050000000001</v>
       </c>
       <c r="G36">
         <v>23.9</v>
@@ -4355,28 +4355,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M36">
-        <v>19.90371560000001</v>
+        <v>20.48911900000001</v>
       </c>
       <c r="N36">
-        <v>26.22961773333333</v>
+        <v>25.64421433333333</v>
       </c>
       <c r="O36">
-        <v>5.403301253066667</v>
+        <v>5.282708152666667</v>
       </c>
       <c r="P36">
-        <v>20.82631648026667</v>
+        <v>20.36150618066667</v>
       </c>
       <c r="Q36">
-        <v>21.02631648026667</v>
+        <v>20.56150618066667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07795316987073832</v>
+        <v>0.07837551420444608</v>
       </c>
       <c r="T36">
-        <v>0.7425674335043493</v>
+        <v>0.7523213442135354</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.317825187038611</v>
+        <v>2.251601610266079</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4401,22 +4401,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07200890423288994</v>
+        <v>0.0721057483510926</v>
       </c>
       <c r="C37">
-        <v>305.8094364820255</v>
+        <v>296.4429311657955</v>
       </c>
       <c r="D37">
-        <v>552.2144364820256</v>
+        <v>550.5709311657956</v>
       </c>
       <c r="E37">
-        <v>-328.895</v>
+        <v>-321.172</v>
       </c>
       <c r="F37">
-        <v>270.3050000000001</v>
+        <v>278.0280000000001</v>
       </c>
       <c r="G37">
         <v>23.9</v>
@@ -4437,28 +4437,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M37">
-        <v>20.48911900000001</v>
+        <v>21.07452240000001</v>
       </c>
       <c r="N37">
-        <v>25.64421433333333</v>
+        <v>25.05881093333333</v>
       </c>
       <c r="O37">
-        <v>5.282708152666667</v>
+        <v>5.162115052266667</v>
       </c>
       <c r="P37">
-        <v>20.36150618066667</v>
+        <v>19.89669588106667</v>
       </c>
       <c r="Q37">
-        <v>20.56150618066667</v>
+        <v>20.09669588106667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07837551420444608</v>
+        <v>0.07881105679858219</v>
       </c>
       <c r="T37">
-        <v>0.7523213442135354</v>
+        <v>0.7623800646323834</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.251601610266079</v>
+        <v>2.189057121092022</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4483,22 +4483,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07210574835109261</v>
+        <v>0.07220259246929527</v>
       </c>
       <c r="C38">
-        <v>296.4429311657954</v>
+        <v>287.0861796493057</v>
       </c>
       <c r="D38">
-        <v>550.5709311657954</v>
+        <v>548.9371796493058</v>
       </c>
       <c r="E38">
-        <v>-321.172</v>
+        <v>-313.449</v>
       </c>
       <c r="F38">
-        <v>278.028</v>
+        <v>285.751</v>
       </c>
       <c r="G38">
         <v>23.9</v>
@@ -4519,28 +4519,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M38">
-        <v>21.0745224</v>
+        <v>21.6599258</v>
       </c>
       <c r="N38">
-        <v>25.05881093333334</v>
+        <v>24.47340753333334</v>
       </c>
       <c r="O38">
-        <v>5.162115052266667</v>
+        <v>5.041521951866668</v>
       </c>
       <c r="P38">
-        <v>19.89669588106667</v>
+        <v>19.43188558146667</v>
       </c>
       <c r="Q38">
-        <v>20.09669588106667</v>
+        <v>19.63188558146667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07881105679858219</v>
+        <v>0.0792604261417385</v>
       </c>
       <c r="T38">
-        <v>0.7623800646323834</v>
+        <v>0.7727581095089727</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.189057121092022</v>
+        <v>2.129893415116562</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4565,22 +4565,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07220259246929527</v>
+        <v>0.07229943658749793</v>
       </c>
       <c r="C39">
-        <v>287.0861796493057</v>
+        <v>277.7390953598473</v>
       </c>
       <c r="D39">
-        <v>548.9371796493058</v>
+        <v>547.3130953598474</v>
       </c>
       <c r="E39">
-        <v>-313.449</v>
+        <v>-305.726</v>
       </c>
       <c r="F39">
-        <v>285.751</v>
+        <v>293.474</v>
       </c>
       <c r="G39">
         <v>23.9</v>
@@ -4601,28 +4601,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M39">
-        <v>21.6599258</v>
+        <v>22.2453292</v>
       </c>
       <c r="N39">
-        <v>24.47340753333334</v>
+        <v>23.88800413333334</v>
       </c>
       <c r="O39">
-        <v>5.041521951866668</v>
+        <v>4.920928851466668</v>
       </c>
       <c r="P39">
-        <v>19.43188558146667</v>
+        <v>18.96707528186667</v>
       </c>
       <c r="Q39">
-        <v>19.63188558146667</v>
+        <v>19.16707528186667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0792604261417385</v>
+        <v>0.07972429127015794</v>
       </c>
       <c r="T39">
-        <v>0.7727581095089727</v>
+        <v>0.7834709300267424</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.129893415116562</v>
+        <v>2.073843588402968</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4647,22 +4647,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07229943658749793</v>
+        <v>0.07239628070570059</v>
       </c>
       <c r="C40">
-        <v>277.7390953598473</v>
+        <v>268.4015927462244</v>
       </c>
       <c r="D40">
-        <v>547.3130953598474</v>
+        <v>545.6985927462244</v>
       </c>
       <c r="E40">
-        <v>-305.726</v>
+        <v>-298.003</v>
       </c>
       <c r="F40">
-        <v>293.474</v>
+        <v>301.1970000000001</v>
       </c>
       <c r="G40">
         <v>23.9</v>
@@ -4683,28 +4683,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M40">
-        <v>22.2453292</v>
+        <v>22.83073260000001</v>
       </c>
       <c r="N40">
-        <v>23.88800413333334</v>
+        <v>23.30260073333333</v>
       </c>
       <c r="O40">
-        <v>4.920928851466668</v>
+        <v>4.800335751066667</v>
       </c>
       <c r="P40">
-        <v>18.96707528186667</v>
+        <v>18.50226498226667</v>
       </c>
       <c r="Q40">
-        <v>19.16707528186667</v>
+        <v>18.70226498226667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07972429127015794</v>
+        <v>0.08020336509131243</v>
       </c>
       <c r="T40">
-        <v>0.7834709300267424</v>
+        <v>0.7945349905614881</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.073843588402968</v>
+        <v>2.020668111777251</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4729,22 +4729,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07239628070570059</v>
+        <v>0.07700304482390324</v>
       </c>
       <c r="C41">
-        <v>268.4015927462244</v>
+        <v>193.5278245104215</v>
       </c>
       <c r="D41">
-        <v>545.6985927462244</v>
+        <v>478.5478245104216</v>
       </c>
       <c r="E41">
-        <v>-298.003</v>
+        <v>-290.28</v>
       </c>
       <c r="F41">
-        <v>301.1970000000001</v>
+        <v>308.9200000000001</v>
       </c>
       <c r="G41">
         <v>23.9</v>
@@ -4765,45 +4765,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M41">
-        <v>22.83073260000001</v>
+        <v>27.8028</v>
       </c>
       <c r="N41">
-        <v>23.30260073333333</v>
+        <v>18.33053333333334</v>
       </c>
       <c r="O41">
-        <v>4.800335751066667</v>
+        <v>3.776089866666667</v>
       </c>
       <c r="P41">
-        <v>18.50226498226667</v>
+        <v>14.55444346666667</v>
       </c>
       <c r="Q41">
-        <v>18.70226498226667</v>
+        <v>14.75444346666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08020336509131243</v>
+        <v>0.08069840803983873</v>
       </c>
       <c r="T41">
-        <v>0.7945349905614881</v>
+        <v>0.8059678531140586</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.206</v>
       </c>
       <c r="W41">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.020668111777251</v>
+        <v>1.659305297787753</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07700304482390324</v>
+        <v>0.07721263694210589</v>
       </c>
       <c r="C42">
-        <v>193.5278245104215</v>
+        <v>183.1405570406374</v>
       </c>
       <c r="D42">
-        <v>478.5478245104216</v>
+        <v>475.8835570406375</v>
       </c>
       <c r="E42">
-        <v>-290.28</v>
+        <v>-282.557</v>
       </c>
       <c r="F42">
-        <v>308.9200000000001</v>
+        <v>316.643</v>
       </c>
       <c r="G42">
         <v>23.9</v>
@@ -4847,28 +4847,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M42">
-        <v>27.8028</v>
+        <v>28.49787</v>
       </c>
       <c r="N42">
-        <v>18.33053333333334</v>
+        <v>17.63546333333334</v>
       </c>
       <c r="O42">
-        <v>3.776089866666667</v>
+        <v>3.632905446666668</v>
       </c>
       <c r="P42">
-        <v>14.55444346666667</v>
+        <v>14.00255788666667</v>
       </c>
       <c r="Q42">
-        <v>14.75444346666667</v>
+        <v>14.20255788666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08069840803983873</v>
+        <v>0.08121023210526424</v>
       </c>
       <c r="T42">
-        <v>0.8059678531140586</v>
+        <v>0.8177882703294281</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.659305297787753</v>
+        <v>1.6188344368661</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4893,22 +4893,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07721263694210589</v>
+        <v>0.07742222906030856</v>
       </c>
       <c r="C43">
-        <v>183.1405570406374</v>
+        <v>172.7827914111803</v>
       </c>
       <c r="D43">
-        <v>475.8835570406375</v>
+        <v>473.2487914111804</v>
       </c>
       <c r="E43">
-        <v>-282.557</v>
+        <v>-274.834</v>
       </c>
       <c r="F43">
-        <v>316.643</v>
+        <v>324.366</v>
       </c>
       <c r="G43">
         <v>23.9</v>
@@ -4929,28 +4929,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M43">
-        <v>28.49787</v>
+        <v>29.19294</v>
       </c>
       <c r="N43">
-        <v>17.63546333333334</v>
+        <v>16.94039333333334</v>
       </c>
       <c r="O43">
-        <v>3.632905446666668</v>
+        <v>3.489721026666667</v>
       </c>
       <c r="P43">
-        <v>14.00255788666667</v>
+        <v>13.45067230666667</v>
       </c>
       <c r="Q43">
-        <v>14.20255788666667</v>
+        <v>13.65067230666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08121023210526424</v>
+        <v>0.08173970527639407</v>
       </c>
       <c r="T43">
-        <v>0.8177882703294281</v>
+        <v>0.8300162881384312</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.6188344368661</v>
+        <v>1.58029075979786</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4975,22 +4975,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07742222906030855</v>
+        <v>0.07763182117851121</v>
       </c>
       <c r="C44">
-        <v>172.7827914111805</v>
+        <v>162.4540403025611</v>
       </c>
       <c r="D44">
-        <v>473.2487914111806</v>
+        <v>470.6430403025611</v>
       </c>
       <c r="E44">
-        <v>-274.834</v>
+        <v>-267.111</v>
       </c>
       <c r="F44">
-        <v>324.366</v>
+        <v>332.089</v>
       </c>
       <c r="G44">
         <v>23.9</v>
@@ -5011,28 +5011,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M44">
-        <v>29.19294</v>
+        <v>29.88801</v>
       </c>
       <c r="N44">
-        <v>16.94039333333334</v>
+        <v>16.24532333333334</v>
       </c>
       <c r="O44">
-        <v>3.489721026666667</v>
+        <v>3.346536606666669</v>
       </c>
       <c r="P44">
-        <v>13.45067230666667</v>
+        <v>12.89878672666667</v>
       </c>
       <c r="Q44">
-        <v>13.65067230666667</v>
+        <v>13.09878672666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08173970527639406</v>
+        <v>0.08228775645352844</v>
       </c>
       <c r="T44">
-        <v>0.8300162881384311</v>
+        <v>0.8426733592038903</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.58029075979786</v>
+        <v>1.543539811895584</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5057,22 +5057,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07763182117851121</v>
+        <v>0.07784141329671387</v>
       </c>
       <c r="C45">
-        <v>162.4540403025611</v>
+        <v>152.1538270694198</v>
       </c>
       <c r="D45">
-        <v>470.6430403025611</v>
+        <v>468.0658270694198</v>
       </c>
       <c r="E45">
-        <v>-267.111</v>
+        <v>-259.388</v>
       </c>
       <c r="F45">
-        <v>332.089</v>
+        <v>339.812</v>
       </c>
       <c r="G45">
         <v>23.9</v>
@@ -5093,28 +5093,28 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M45">
-        <v>29.88801</v>
+        <v>30.58308</v>
       </c>
       <c r="N45">
-        <v>16.24532333333334</v>
+        <v>15.55025333333334</v>
       </c>
       <c r="O45">
-        <v>3.346536606666669</v>
+        <v>3.203352186666669</v>
       </c>
       <c r="P45">
-        <v>12.89878672666667</v>
+        <v>12.34690114666667</v>
       </c>
       <c r="Q45">
-        <v>13.09878672666667</v>
+        <v>12.54690114666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08228775645352844</v>
+        <v>0.08285538088698906</v>
       </c>
       <c r="T45">
-        <v>0.8426733592038903</v>
+        <v>0.8557824685216874</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.543539811895584</v>
+        <v>1.50845936162523</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5139,22 +5139,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07784141329671387</v>
+        <v>0.09985113498904602</v>
       </c>
       <c r="C46">
-        <v>152.1538270694198</v>
+        <v>-26.45796034413604</v>
       </c>
       <c r="D46">
-        <v>468.0658270694198</v>
+        <v>297.177039655864</v>
       </c>
       <c r="E46">
-        <v>-259.388</v>
+        <v>-251.665</v>
       </c>
       <c r="F46">
-        <v>339.812</v>
+        <v>347.535</v>
       </c>
       <c r="G46">
         <v>23.9</v>
@@ -5175,45 +5175,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M46">
-        <v>30.58308</v>
+        <v>51.01813800000001</v>
       </c>
       <c r="N46">
-        <v>15.55025333333334</v>
+        <v>-4.884804666666668</v>
       </c>
       <c r="O46">
-        <v>3.203352186666669</v>
+        <v>-1.006269761333334</v>
       </c>
       <c r="P46">
-        <v>12.34690114666667</v>
+        <v>-3.878534905333334</v>
       </c>
       <c r="Q46">
-        <v>12.54690114666667</v>
+        <v>-3.678534905333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08285538088698906</v>
+        <v>0.08381189650443635</v>
       </c>
       <c r="T46">
-        <v>0.8557824685216874</v>
+        <v>0.8778728984858283</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.206</v>
+        <v>0.1862762350650012</v>
       </c>
       <c r="W46">
-        <v>0.07146</v>
+        <v>0.1194546486924579</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.50845936162523</v>
+        <v>0.9042535682767046</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5221,22 +5221,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09985113498904602</v>
+        <v>0.100861134989046</v>
       </c>
       <c r="C47">
-        <v>-26.45796034413604</v>
+        <v>-39.0777663791099</v>
       </c>
       <c r="D47">
-        <v>297.177039655864</v>
+        <v>292.2802336208902</v>
       </c>
       <c r="E47">
-        <v>-251.665</v>
+        <v>-243.942</v>
       </c>
       <c r="F47">
-        <v>347.535</v>
+        <v>355.258</v>
       </c>
       <c r="G47">
         <v>23.9</v>
@@ -5257,37 +5257,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M47">
-        <v>51.01813800000001</v>
+        <v>52.15187440000001</v>
       </c>
       <c r="N47">
-        <v>-4.884804666666668</v>
+        <v>-6.018541066666671</v>
       </c>
       <c r="O47">
-        <v>-1.006269761333334</v>
+        <v>-1.239819459733334</v>
       </c>
       <c r="P47">
-        <v>-3.878534905333334</v>
+        <v>-4.778721606933336</v>
       </c>
       <c r="Q47">
-        <v>-3.678534905333334</v>
+        <v>-4.578721606933337</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08381189650443635</v>
+        <v>0.08451582051377776</v>
       </c>
       <c r="T47">
-        <v>0.8778728984858283</v>
+        <v>0.8941298040133436</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1862762350650012</v>
+        <v>0.1822267516940228</v>
       </c>
       <c r="W47">
-        <v>0.1194546486924579</v>
+        <v>0.1200491128513175</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9042535682767046</v>
+        <v>0.8845958820098195</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5303,22 +5303,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.100861134989046</v>
+        <v>0.101871134989046</v>
       </c>
       <c r="C48">
-        <v>-39.0777663791099</v>
+        <v>-51.53881183493257</v>
       </c>
       <c r="D48">
-        <v>292.2802336208902</v>
+        <v>287.5421881650675</v>
       </c>
       <c r="E48">
-        <v>-243.942</v>
+        <v>-236.219</v>
       </c>
       <c r="F48">
-        <v>355.258</v>
+        <v>362.9810000000001</v>
       </c>
       <c r="G48">
         <v>23.9</v>
@@ -5339,37 +5339,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M48">
-        <v>52.15187440000001</v>
+        <v>53.28561080000001</v>
       </c>
       <c r="N48">
-        <v>-6.018541066666671</v>
+        <v>-7.152277466666675</v>
       </c>
       <c r="O48">
-        <v>-1.239819459733334</v>
+        <v>-1.473369158133335</v>
       </c>
       <c r="P48">
-        <v>-4.778721606933336</v>
+        <v>-5.678908308533339</v>
       </c>
       <c r="Q48">
-        <v>-4.578721606933337</v>
+        <v>-5.47890830853334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08451582051377776</v>
+        <v>0.08524630769328301</v>
       </c>
       <c r="T48">
-        <v>0.8941298040133436</v>
+        <v>0.9110001776739728</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1822267516940228</v>
+        <v>0.1783495867643628</v>
       </c>
       <c r="W48">
-        <v>0.1200491128513175</v>
+        <v>0.1206182806629916</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8845958820098195</v>
+        <v>0.8657746930308872</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5385,22 +5385,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.101871134989046</v>
+        <v>0.102881134989046</v>
       </c>
       <c r="C49">
-        <v>-51.53881183493257</v>
+        <v>-63.84869437370361</v>
       </c>
       <c r="D49">
-        <v>287.5421881650675</v>
+        <v>282.9553056262965</v>
       </c>
       <c r="E49">
-        <v>-236.219</v>
+        <v>-228.496</v>
       </c>
       <c r="F49">
-        <v>362.9810000000001</v>
+        <v>370.7040000000001</v>
       </c>
       <c r="G49">
         <v>23.9</v>
@@ -5421,37 +5421,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M49">
-        <v>53.28561080000001</v>
+        <v>54.41934720000001</v>
       </c>
       <c r="N49">
-        <v>-7.152277466666675</v>
+        <v>-8.286013866666671</v>
       </c>
       <c r="O49">
-        <v>-1.473369158133335</v>
+        <v>-1.706918856533334</v>
       </c>
       <c r="P49">
-        <v>-5.678908308533339</v>
+        <v>-6.579095010133337</v>
       </c>
       <c r="Q49">
-        <v>-5.47890830853334</v>
+        <v>-6.379095010133337</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08524630769328301</v>
+        <v>0.08600489053353846</v>
       </c>
       <c r="T49">
-        <v>0.9110001776739728</v>
+        <v>0.9285194118600107</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1783495867643628</v>
+        <v>0.1746339703734386</v>
       </c>
       <c r="W49">
-        <v>0.1206182806629916</v>
+        <v>0.1211637331491792</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8657746930308872</v>
+        <v>0.8477377202594104</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5467,22 +5467,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.102881134989046</v>
+        <v>0.103891134989046</v>
       </c>
       <c r="C50">
-        <v>-63.84869437370338</v>
+        <v>-76.0145344768909</v>
       </c>
       <c r="D50">
-        <v>282.9553056262966</v>
+        <v>278.5124655231091</v>
       </c>
       <c r="E50">
-        <v>-228.496</v>
+        <v>-220.773</v>
       </c>
       <c r="F50">
-        <v>370.704</v>
+        <v>378.427</v>
       </c>
       <c r="G50">
         <v>23.9</v>
@@ -5503,37 +5503,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M50">
-        <v>54.4193472</v>
+        <v>55.55308360000001</v>
       </c>
       <c r="N50">
-        <v>-8.286013866666664</v>
+        <v>-9.419750266666668</v>
       </c>
       <c r="O50">
-        <v>-1.706918856533333</v>
+        <v>-1.940468554933334</v>
       </c>
       <c r="P50">
-        <v>-6.579095010133331</v>
+        <v>-7.479281711733334</v>
       </c>
       <c r="Q50">
-        <v>-6.379095010133332</v>
+        <v>-7.279281711733335</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08600489053353846</v>
+        <v>0.08679322172047058</v>
       </c>
       <c r="T50">
-        <v>0.9285194118600107</v>
+        <v>0.9467256748376579</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1746339703734386</v>
+        <v>0.1710700117943888</v>
       </c>
       <c r="W50">
-        <v>0.1211637331491792</v>
+        <v>0.1216869222685837</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8477377202594105</v>
+        <v>0.8304369504581981</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5549,22 +5549,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.103891134989046</v>
+        <v>0.104901134989046</v>
       </c>
       <c r="C51">
-        <v>-76.0145344768909</v>
+        <v>-88.04301232861081</v>
       </c>
       <c r="D51">
-        <v>278.5124655231091</v>
+        <v>274.2069876713892</v>
       </c>
       <c r="E51">
-        <v>-220.773</v>
+        <v>-213.05</v>
       </c>
       <c r="F51">
-        <v>378.427</v>
+        <v>386.15</v>
       </c>
       <c r="G51">
         <v>23.9</v>
@@ -5585,37 +5585,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M51">
-        <v>55.55308360000001</v>
+        <v>56.68682000000001</v>
       </c>
       <c r="N51">
-        <v>-9.419750266666668</v>
+        <v>-10.55348666666667</v>
       </c>
       <c r="O51">
-        <v>-1.940468554933334</v>
+        <v>-2.174018253333335</v>
       </c>
       <c r="P51">
-        <v>-7.479281711733334</v>
+        <v>-8.379468413333337</v>
       </c>
       <c r="Q51">
-        <v>-7.279281711733335</v>
+        <v>-8.179468413333337</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08679322172047058</v>
+        <v>0.08761308615488</v>
       </c>
       <c r="T51">
-        <v>0.9467256748376579</v>
+        <v>0.9656601883344111</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1710700117943888</v>
+        <v>0.167648611558501</v>
       </c>
       <c r="W51">
-        <v>0.1216869222685837</v>
+        <v>0.1221891838232121</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8304369504581981</v>
+        <v>0.8138282114490341</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.104901134989046</v>
+        <v>0.1339655379720703</v>
       </c>
       <c r="C52">
-        <v>-88.04301232861081</v>
+        <v>-180.1911032595511</v>
       </c>
       <c r="D52">
-        <v>274.2069876713892</v>
+        <v>189.781896740449</v>
       </c>
       <c r="E52">
-        <v>-213.05</v>
+        <v>-205.327</v>
       </c>
       <c r="F52">
-        <v>386.15</v>
+        <v>393.873</v>
       </c>
       <c r="G52">
         <v>23.9</v>
@@ -5667,45 +5667,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M52">
-        <v>56.68682000000001</v>
+        <v>79.08969840000002</v>
       </c>
       <c r="N52">
-        <v>-10.55348666666667</v>
+        <v>-32.95636506666668</v>
       </c>
       <c r="O52">
-        <v>-2.174018253333335</v>
+        <v>-6.789011203733336</v>
       </c>
       <c r="P52">
-        <v>-8.379468413333337</v>
+        <v>-26.16735386293334</v>
       </c>
       <c r="Q52">
-        <v>-8.179468413333337</v>
+        <v>-25.96735386293334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08761308615488</v>
+        <v>0.08951621644992708</v>
       </c>
       <c r="T52">
-        <v>0.9656601883344111</v>
+        <v>1.009612389143812</v>
       </c>
       <c r="U52">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.167648611558501</v>
+        <v>0.1201606133153072</v>
       </c>
       <c r="W52">
-        <v>0.1221891838232121</v>
+        <v>0.1766717488462863</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8138282114490341</v>
+        <v>0.5833039481325589</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5713,22 +5713,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1339655379720703</v>
+        <v>0.1355155379720703</v>
       </c>
       <c r="C53">
-        <v>-180.1911032595511</v>
+        <v>-190.9799119483789</v>
       </c>
       <c r="D53">
-        <v>189.781896740449</v>
+        <v>186.7160880516211</v>
       </c>
       <c r="E53">
-        <v>-205.327</v>
+        <v>-197.604</v>
       </c>
       <c r="F53">
-        <v>393.873</v>
+        <v>401.5960000000001</v>
       </c>
       <c r="G53">
         <v>23.9</v>
@@ -5749,37 +5749,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M53">
-        <v>79.08969840000002</v>
+        <v>80.64047680000002</v>
       </c>
       <c r="N53">
-        <v>-32.95636506666668</v>
+        <v>-34.50714346666668</v>
       </c>
       <c r="O53">
-        <v>-6.789011203733336</v>
+        <v>-7.108471554133335</v>
       </c>
       <c r="P53">
-        <v>-26.16735386293334</v>
+        <v>-27.39867191253334</v>
       </c>
       <c r="Q53">
-        <v>-25.96735386293334</v>
+        <v>-27.19867191253334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08951621644992708</v>
+        <v>0.09042697095930055</v>
       </c>
       <c r="T53">
-        <v>1.009612389143812</v>
+        <v>1.030645980584309</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1201606133153072</v>
+        <v>0.1178498322900128</v>
       </c>
       <c r="W53">
-        <v>0.1766717488462863</v>
+        <v>0.1771357536761654</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5833039481325589</v>
+        <v>0.5720865645146251</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1355155379720703</v>
+        <v>0.1370655379720703</v>
       </c>
       <c r="C54">
-        <v>-190.9799119483789</v>
+        <v>-201.6712428591272</v>
       </c>
       <c r="D54">
-        <v>186.7160880516211</v>
+        <v>183.7477571408729</v>
       </c>
       <c r="E54">
-        <v>-197.604</v>
+        <v>-189.881</v>
       </c>
       <c r="F54">
-        <v>401.5960000000001</v>
+        <v>409.3190000000001</v>
       </c>
       <c r="G54">
         <v>23.9</v>
@@ -5831,37 +5831,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M54">
-        <v>80.64047680000002</v>
+        <v>82.19125520000001</v>
       </c>
       <c r="N54">
-        <v>-34.50714346666668</v>
+        <v>-36.05792186666667</v>
       </c>
       <c r="O54">
-        <v>-7.108471554133335</v>
+        <v>-7.427931904533335</v>
       </c>
       <c r="P54">
-        <v>-27.39867191253334</v>
+        <v>-28.62998996213334</v>
       </c>
       <c r="Q54">
-        <v>-27.19867191253334</v>
+        <v>-28.42998996213334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09042697095930055</v>
+        <v>0.09137648097971121</v>
       </c>
       <c r="T54">
-        <v>1.030645980584309</v>
+        <v>1.052574618469081</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1178498322900128</v>
+        <v>0.1156262505486918</v>
       </c>
       <c r="W54">
-        <v>0.1771357536761654</v>
+        <v>0.1775822488898227</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5720865645146251</v>
+        <v>0.5612924783917077</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1370655379720703</v>
+        <v>0.1386155379720703</v>
       </c>
       <c r="C55">
-        <v>-201.6712428591272</v>
+        <v>-212.2696722185103</v>
       </c>
       <c r="D55">
-        <v>183.7477571408729</v>
+        <v>180.8723277814898</v>
       </c>
       <c r="E55">
-        <v>-189.881</v>
+        <v>-182.158</v>
       </c>
       <c r="F55">
-        <v>409.3190000000001</v>
+        <v>417.0420000000001</v>
       </c>
       <c r="G55">
         <v>23.9</v>
@@ -5913,37 +5913,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M55">
-        <v>82.19125520000001</v>
+        <v>83.74203360000001</v>
       </c>
       <c r="N55">
-        <v>-36.05792186666667</v>
+        <v>-37.60870026666667</v>
       </c>
       <c r="O55">
-        <v>-7.427931904533335</v>
+        <v>-7.747392254933335</v>
       </c>
       <c r="P55">
-        <v>-28.62998996213334</v>
+        <v>-29.86130801173334</v>
       </c>
       <c r="Q55">
-        <v>-28.42998996213334</v>
+        <v>-29.66130801173334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09137648097971121</v>
+        <v>0.09236727404448754</v>
       </c>
       <c r="T55">
-        <v>1.052574618469081</v>
+        <v>1.075456675392322</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1156262505486918</v>
+        <v>0.113485023686679</v>
       </c>
       <c r="W55">
-        <v>0.1775822488898227</v>
+        <v>0.1780122072437149</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5612924783917077</v>
+        <v>0.5508981732363056</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5959,22 +5959,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1386155379720703</v>
+        <v>0.1401655379720703</v>
       </c>
       <c r="C56">
-        <v>-212.2696722185103</v>
+        <v>-222.7794942171913</v>
       </c>
       <c r="D56">
-        <v>180.8723277814898</v>
+        <v>178.0855057828088</v>
       </c>
       <c r="E56">
-        <v>-182.158</v>
+        <v>-174.4349999999999</v>
       </c>
       <c r="F56">
-        <v>417.0420000000001</v>
+        <v>424.7650000000001</v>
       </c>
       <c r="G56">
         <v>23.9</v>
@@ -5995,37 +5995,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M56">
-        <v>83.74203360000001</v>
+        <v>85.29281200000003</v>
       </c>
       <c r="N56">
-        <v>-37.60870026666667</v>
+        <v>-39.15947866666669</v>
       </c>
       <c r="O56">
-        <v>-7.747392254933335</v>
+        <v>-8.066852605333338</v>
       </c>
       <c r="P56">
-        <v>-29.86130801173334</v>
+        <v>-31.09262606133335</v>
       </c>
       <c r="Q56">
-        <v>-29.66130801173334</v>
+        <v>-30.89262606133335</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09236727404448754</v>
+        <v>0.09340210235658727</v>
       </c>
       <c r="T56">
-        <v>1.075456675392322</v>
+        <v>1.099355712623263</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.113485023686679</v>
+        <v>0.1114216596196484</v>
       </c>
       <c r="W56">
-        <v>0.1780122072437149</v>
+        <v>0.1784265307483746</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5508981732363056</v>
+        <v>0.5408818428138273</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6041,22 +6041,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1401655379720703</v>
+        <v>0.1417155379720703</v>
       </c>
       <c r="C57">
-        <v>-222.7794942171913</v>
+        <v>-233.2047424076887</v>
       </c>
       <c r="D57">
-        <v>178.0855057828088</v>
+        <v>175.3832575923113</v>
       </c>
       <c r="E57">
-        <v>-174.4349999999999</v>
+        <v>-166.712</v>
       </c>
       <c r="F57">
-        <v>424.7650000000001</v>
+        <v>432.4880000000001</v>
       </c>
       <c r="G57">
         <v>23.9</v>
@@ -6077,37 +6077,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M57">
-        <v>85.29281200000003</v>
+        <v>86.84359040000001</v>
       </c>
       <c r="N57">
-        <v>-39.15947866666669</v>
+        <v>-40.71025706666667</v>
       </c>
       <c r="O57">
-        <v>-8.066852605333338</v>
+        <v>-8.386312955733334</v>
       </c>
       <c r="P57">
-        <v>-31.09262606133335</v>
+        <v>-32.32394411093334</v>
       </c>
       <c r="Q57">
-        <v>-30.89262606133335</v>
+        <v>-32.12394411093334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09340210235658727</v>
+        <v>0.09448396831923697</v>
       </c>
       <c r="T57">
-        <v>1.099355712623263</v>
+        <v>1.124341069728337</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1114216596196484</v>
+        <v>0.1094319871264404</v>
       </c>
       <c r="W57">
-        <v>0.1784265307483746</v>
+        <v>0.1788260569850108</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5408818428138273</v>
+        <v>0.5312232384778662</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6123,22 +6123,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1417155379720703</v>
+        <v>0.1432655379720703</v>
       </c>
       <c r="C58">
-        <v>-233.2047424076887</v>
+        <v>-243.5492091832666</v>
       </c>
       <c r="D58">
-        <v>175.3832575923113</v>
+        <v>172.7617908167335</v>
       </c>
       <c r="E58">
-        <v>-166.712</v>
+        <v>-158.989</v>
       </c>
       <c r="F58">
-        <v>432.4880000000001</v>
+        <v>440.2110000000001</v>
       </c>
       <c r="G58">
         <v>23.9</v>
@@ -6159,37 +6159,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M58">
-        <v>86.84359040000001</v>
+        <v>88.39436880000002</v>
       </c>
       <c r="N58">
-        <v>-40.71025706666667</v>
+        <v>-42.26103546666668</v>
       </c>
       <c r="O58">
-        <v>-8.386312955733334</v>
+        <v>-8.705773306133338</v>
       </c>
       <c r="P58">
-        <v>-32.32394411093334</v>
+        <v>-33.55526216053335</v>
       </c>
       <c r="Q58">
-        <v>-32.12394411093334</v>
+        <v>-33.35526216053334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09448396831923697</v>
+        <v>0.09561615362898668</v>
       </c>
       <c r="T58">
-        <v>1.124341069728337</v>
+        <v>1.150488536466205</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1094319871264404</v>
+        <v>0.1075121277031695</v>
       </c>
       <c r="W58">
-        <v>0.1788260569850108</v>
+        <v>0.1792115647572036</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5312232384778662</v>
+        <v>0.5219035325396579</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6205,22 +6205,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1432655379720703</v>
+        <v>0.1448155379720703</v>
       </c>
       <c r="C59">
-        <v>-243.5492091832666</v>
+        <v>-253.8164635356365</v>
       </c>
       <c r="D59">
-        <v>172.7617908167335</v>
+        <v>170.2175364643636</v>
       </c>
       <c r="E59">
-        <v>-158.989</v>
+        <v>-151.266</v>
       </c>
       <c r="F59">
-        <v>440.2110000000001</v>
+        <v>447.9340000000001</v>
       </c>
       <c r="G59">
         <v>23.9</v>
@@ -6241,37 +6241,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M59">
-        <v>88.39436880000002</v>
+        <v>89.94514720000002</v>
       </c>
       <c r="N59">
-        <v>-42.26103546666668</v>
+        <v>-43.81181386666668</v>
       </c>
       <c r="O59">
-        <v>-8.705773306133338</v>
+        <v>-9.025233656533338</v>
       </c>
       <c r="P59">
-        <v>-33.55526216053335</v>
+        <v>-34.78658021013334</v>
       </c>
       <c r="Q59">
-        <v>-33.35526216053334</v>
+        <v>-34.58658021013335</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09561615362898668</v>
+        <v>0.09680225252491492</v>
       </c>
       <c r="T59">
-        <v>1.150488536466205</v>
+        <v>1.177881120667781</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1075121277031695</v>
+        <v>0.105658470328977</v>
       </c>
       <c r="W59">
-        <v>0.1792115647572036</v>
+        <v>0.1795837791579414</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5219035325396579</v>
+        <v>0.5129051957717328</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6287,22 +6287,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1448155379720703</v>
+        <v>0.1463655379720703</v>
       </c>
       <c r="C60">
-        <v>-253.8164635356364</v>
+        <v>-264.0098672663314</v>
       </c>
       <c r="D60">
-        <v>170.2175364643636</v>
+        <v>167.7471327336686</v>
       </c>
       <c r="E60">
-        <v>-151.266</v>
+        <v>-143.543</v>
       </c>
       <c r="F60">
-        <v>447.934</v>
+        <v>455.657</v>
       </c>
       <c r="G60">
         <v>23.9</v>
@@ -6323,37 +6323,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M60">
-        <v>89.94514720000001</v>
+        <v>91.49592560000001</v>
       </c>
       <c r="N60">
-        <v>-43.81181386666667</v>
+        <v>-45.36259226666667</v>
       </c>
       <c r="O60">
-        <v>-9.025233656533334</v>
+        <v>-9.344694006933334</v>
       </c>
       <c r="P60">
-        <v>-34.78658021013334</v>
+        <v>-36.01789825973333</v>
       </c>
       <c r="Q60">
-        <v>-34.58658021013333</v>
+        <v>-35.81789825973333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09680225252491491</v>
+        <v>0.09804620990357135</v>
       </c>
       <c r="T60">
-        <v>1.177881120667781</v>
+        <v>1.206609928488946</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.105658470328977</v>
+        <v>0.1038676487979774</v>
       </c>
       <c r="W60">
-        <v>0.1795837791579414</v>
+        <v>0.1799433761213662</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.512905195771733</v>
+        <v>0.5042118873688222</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6369,22 +6369,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1463655379720703</v>
+        <v>0.1691231057890196</v>
       </c>
       <c r="C61">
-        <v>-264.0098672663314</v>
+        <v>-301.1988407049233</v>
       </c>
       <c r="D61">
-        <v>167.7471327336686</v>
+        <v>138.2811592950766</v>
       </c>
       <c r="E61">
-        <v>-143.543</v>
+        <v>-135.8200000000001</v>
       </c>
       <c r="F61">
-        <v>455.657</v>
+        <v>463.38</v>
       </c>
       <c r="G61">
         <v>23.9</v>
@@ -6405,45 +6405,45 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M61">
-        <v>91.49592560000001</v>
+        <v>109.265004</v>
       </c>
       <c r="N61">
-        <v>-45.36259226666667</v>
+        <v>-63.13167066666666</v>
       </c>
       <c r="O61">
-        <v>-9.344694006933334</v>
+        <v>-13.00512415733333</v>
       </c>
       <c r="P61">
-        <v>-36.01789825973333</v>
+        <v>-50.12654650933333</v>
       </c>
       <c r="Q61">
-        <v>-35.81789825973333</v>
+        <v>-49.92654650933333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09804620990357135</v>
+        <v>0.09987128469353387</v>
       </c>
       <c r="T61">
-        <v>1.206609928488946</v>
+        <v>1.248759461744432</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1038676487979774</v>
+        <v>0.08697630823009597</v>
       </c>
       <c r="W61">
-        <v>0.1799433761213662</v>
+        <v>0.2152909865193434</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5042118873688222</v>
+        <v>0.4222150884956114</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6451,22 +6451,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1691231057890196</v>
+        <v>0.1710231057890196</v>
       </c>
       <c r="C62">
-        <v>-301.1988407049233</v>
+        <v>-310.9204762650718</v>
       </c>
       <c r="D62">
-        <v>138.2811592950766</v>
+        <v>136.2825237349282</v>
       </c>
       <c r="E62">
-        <v>-135.8200000000001</v>
+        <v>-128.097</v>
       </c>
       <c r="F62">
-        <v>463.38</v>
+        <v>471.103</v>
       </c>
       <c r="G62">
         <v>23.9</v>
@@ -6487,37 +6487,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M62">
-        <v>109.265004</v>
+        <v>111.0860874</v>
       </c>
       <c r="N62">
-        <v>-63.13167066666666</v>
+        <v>-64.95275406666667</v>
       </c>
       <c r="O62">
-        <v>-13.00512415733333</v>
+        <v>-13.38026733773333</v>
       </c>
       <c r="P62">
-        <v>-50.12654650933333</v>
+        <v>-51.57248672893333</v>
       </c>
       <c r="Q62">
-        <v>-49.92654650933333</v>
+        <v>-51.37248672893334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09987128469353387</v>
+        <v>0.101257727890804</v>
       </c>
       <c r="T62">
-        <v>1.248759461744432</v>
+        <v>1.280778935122494</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08697630823009597</v>
+        <v>0.0855504671115698</v>
       </c>
       <c r="W62">
-        <v>0.2152909865193434</v>
+        <v>0.2156271998550919</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4222150884956114</v>
+        <v>0.4152935296678145</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6533,22 +6533,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1710231057890196</v>
+        <v>0.1729231057890196</v>
       </c>
       <c r="C63">
-        <v>-310.9204762650718</v>
+        <v>-320.5851607282157</v>
       </c>
       <c r="D63">
-        <v>136.2825237349282</v>
+        <v>134.3408392717843</v>
       </c>
       <c r="E63">
-        <v>-128.097</v>
+        <v>-120.374</v>
       </c>
       <c r="F63">
-        <v>471.103</v>
+        <v>478.826</v>
       </c>
       <c r="G63">
         <v>23.9</v>
@@ -6569,37 +6569,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M63">
-        <v>111.0860874</v>
+        <v>112.9071708</v>
       </c>
       <c r="N63">
-        <v>-64.95275406666667</v>
+        <v>-66.77383746666666</v>
       </c>
       <c r="O63">
-        <v>-13.38026733773333</v>
+        <v>-13.75541051813333</v>
       </c>
       <c r="P63">
-        <v>-51.57248672893333</v>
+        <v>-53.01842694853333</v>
       </c>
       <c r="Q63">
-        <v>-51.37248672893334</v>
+        <v>-52.81842694853333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.101257727890804</v>
+        <v>0.1027171417826672</v>
       </c>
       <c r="T63">
-        <v>1.280778935122494</v>
+        <v>1.314483643941507</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0855504671115698</v>
+        <v>0.08417062086783481</v>
       </c>
       <c r="W63">
-        <v>0.2156271998550919</v>
+        <v>0.2159525675993646</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4152935296678145</v>
+        <v>0.4085952469312368</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6615,22 +6615,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1729231057890196</v>
+        <v>0.1748231057890196</v>
       </c>
       <c r="C64">
-        <v>-320.5851607282157</v>
+        <v>-330.1952941311137</v>
       </c>
       <c r="D64">
-        <v>134.3408392717843</v>
+        <v>132.4537058688863</v>
       </c>
       <c r="E64">
-        <v>-120.374</v>
+        <v>-112.651</v>
       </c>
       <c r="F64">
-        <v>478.826</v>
+        <v>486.549</v>
       </c>
       <c r="G64">
         <v>23.9</v>
@@ -6651,37 +6651,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M64">
-        <v>112.9071708</v>
+        <v>114.7282542</v>
       </c>
       <c r="N64">
-        <v>-66.77383746666666</v>
+        <v>-68.59492086666667</v>
       </c>
       <c r="O64">
-        <v>-13.75541051813333</v>
+        <v>-14.13055369853334</v>
       </c>
       <c r="P64">
-        <v>-53.01842694853333</v>
+        <v>-54.46436716813334</v>
       </c>
       <c r="Q64">
-        <v>-52.81842694853333</v>
+        <v>-54.26436716813333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1027171417826672</v>
+        <v>0.1042554429119285</v>
       </c>
       <c r="T64">
-        <v>1.314483643941507</v>
+        <v>1.350010228912899</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08417062086783481</v>
+        <v>0.08283457926675805</v>
       </c>
       <c r="W64">
-        <v>0.2159525675993646</v>
+        <v>0.2162676062088985</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4085952469312368</v>
+        <v>0.4021096080910584</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6697,22 +6697,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1748231057890196</v>
+        <v>0.1767231057890196</v>
       </c>
       <c r="C65">
-        <v>-330.1952941311137</v>
+        <v>-339.7531435219927</v>
       </c>
       <c r="D65">
-        <v>132.4537058688863</v>
+        <v>130.6188564780073</v>
       </c>
       <c r="E65">
-        <v>-112.651</v>
+        <v>-104.928</v>
       </c>
       <c r="F65">
-        <v>486.549</v>
+        <v>494.272</v>
       </c>
       <c r="G65">
         <v>23.9</v>
@@ -6733,37 +6733,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M65">
-        <v>114.7282542</v>
+        <v>116.5493376</v>
       </c>
       <c r="N65">
-        <v>-68.59492086666667</v>
+        <v>-70.41600426666668</v>
       </c>
       <c r="O65">
-        <v>-14.13055369853334</v>
+        <v>-14.50569687893334</v>
       </c>
       <c r="P65">
-        <v>-54.46436716813334</v>
+        <v>-55.91030738773334</v>
       </c>
       <c r="Q65">
-        <v>-54.26436716813333</v>
+        <v>-55.71030738773334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1042554429119285</v>
+        <v>0.1058792052150376</v>
       </c>
       <c r="T65">
-        <v>1.350010228912899</v>
+        <v>1.387510513049369</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08283457926675805</v>
+        <v>0.08154028896571495</v>
       </c>
       <c r="W65">
-        <v>0.2162676062088985</v>
+        <v>0.2165727998618844</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4021096080910584</v>
+        <v>0.3958266454646356</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1767231057890196</v>
+        <v>0.1786231057890196</v>
       </c>
       <c r="C66">
-        <v>-339.7531435219927</v>
+        <v>-349.2608520459796</v>
       </c>
       <c r="D66">
-        <v>130.6188564780073</v>
+        <v>128.8341479540204</v>
       </c>
       <c r="E66">
-        <v>-104.928</v>
+        <v>-97.20499999999998</v>
       </c>
       <c r="F66">
-        <v>494.272</v>
+        <v>501.9950000000001</v>
       </c>
       <c r="G66">
         <v>23.9</v>
@@ -6815,37 +6815,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M66">
-        <v>116.5493376</v>
+        <v>118.370421</v>
       </c>
       <c r="N66">
-        <v>-70.41600426666668</v>
+        <v>-72.23708766666668</v>
       </c>
       <c r="O66">
-        <v>-14.50569687893334</v>
+        <v>-14.88084005933334</v>
       </c>
       <c r="P66">
-        <v>-55.91030738773334</v>
+        <v>-57.35624760733334</v>
       </c>
       <c r="Q66">
-        <v>-55.71030738773334</v>
+        <v>-57.15624760733334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1058792052150376</v>
+        <v>0.1075957539354673</v>
       </c>
       <c r="T66">
-        <v>1.387510513049369</v>
+        <v>1.427153670565065</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08154028896571495</v>
+        <v>0.08028582298162704</v>
       </c>
       <c r="W66">
-        <v>0.2165727998618844</v>
+        <v>0.2168686029409324</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3958266454646356</v>
+        <v>0.3897370047651797</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6861,22 +6861,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1786231057890196</v>
+        <v>0.1805231057890196</v>
       </c>
       <c r="C67">
-        <v>-349.2608520459796</v>
+        <v>-358.7204472957424</v>
       </c>
       <c r="D67">
-        <v>128.8341479540204</v>
+        <v>127.0975527042577</v>
       </c>
       <c r="E67">
-        <v>-97.20499999999998</v>
+        <v>-89.48199999999997</v>
       </c>
       <c r="F67">
-        <v>501.9950000000001</v>
+        <v>509.7180000000001</v>
       </c>
       <c r="G67">
         <v>23.9</v>
@@ -6897,37 +6897,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M67">
-        <v>118.370421</v>
+        <v>120.1915044</v>
       </c>
       <c r="N67">
-        <v>-72.23708766666668</v>
+        <v>-74.05817106666669</v>
       </c>
       <c r="O67">
-        <v>-14.88084005933334</v>
+        <v>-15.25598323973334</v>
       </c>
       <c r="P67">
-        <v>-57.35624760733334</v>
+        <v>-58.80218782693335</v>
       </c>
       <c r="Q67">
-        <v>-57.15624760733334</v>
+        <v>-58.60218782693335</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1075957539354673</v>
+        <v>0.1094132761100399</v>
       </c>
       <c r="T67">
-        <v>1.427153670565065</v>
+        <v>1.469128778522861</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08028582298162704</v>
+        <v>0.07906937111826905</v>
       </c>
       <c r="W67">
-        <v>0.2168686029409324</v>
+        <v>0.2171554422903122</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3897370047651797</v>
+        <v>0.383831898632374</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1805231057890196</v>
+        <v>0.1824231057890196</v>
       </c>
       <c r="C68">
-        <v>-358.7204472957424</v>
+        <v>-368.1338489957482</v>
       </c>
       <c r="D68">
-        <v>127.0975527042577</v>
+        <v>125.4071510042519</v>
       </c>
       <c r="E68">
-        <v>-89.48199999999997</v>
+        <v>-81.75900000000001</v>
       </c>
       <c r="F68">
-        <v>509.7180000000001</v>
+        <v>517.441</v>
       </c>
       <c r="G68">
         <v>23.9</v>
@@ -6979,37 +6979,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M68">
-        <v>120.1915044</v>
+        <v>122.0125878</v>
       </c>
       <c r="N68">
-        <v>-74.05817106666669</v>
+        <v>-75.87925446666667</v>
       </c>
       <c r="O68">
-        <v>-15.25598323973334</v>
+        <v>-15.63112642013333</v>
       </c>
       <c r="P68">
-        <v>-58.80218782693335</v>
+        <v>-60.24812804653333</v>
       </c>
       <c r="Q68">
-        <v>-58.60218782693335</v>
+        <v>-60.04812804653334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1094132761100399</v>
+        <v>0.1113409511436775</v>
       </c>
       <c r="T68">
-        <v>1.469128778522861</v>
+        <v>1.513647832417493</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07906937111826905</v>
+        <v>0.07788923125083221</v>
       </c>
       <c r="W68">
-        <v>0.2171554422903122</v>
+        <v>0.2174337192710538</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.383831898632374</v>
+        <v>0.3781030643244282</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7025,22 +7025,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1824231057890196</v>
+        <v>0.1843231057890196</v>
       </c>
       <c r="C69">
-        <v>-368.1338489957482</v>
+        <v>-377.502876081364</v>
       </c>
       <c r="D69">
-        <v>125.4071510042519</v>
+        <v>123.7611239186361</v>
       </c>
       <c r="E69">
-        <v>-81.75900000000001</v>
+        <v>-74.03599999999994</v>
       </c>
       <c r="F69">
-        <v>517.441</v>
+        <v>525.1640000000001</v>
       </c>
       <c r="G69">
         <v>23.9</v>
@@ -7061,37 +7061,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M69">
-        <v>122.0125878</v>
+        <v>123.8336712</v>
       </c>
       <c r="N69">
-        <v>-75.87925446666667</v>
+        <v>-77.70033786666669</v>
       </c>
       <c r="O69">
-        <v>-15.63112642013333</v>
+        <v>-16.00626960053334</v>
       </c>
       <c r="P69">
-        <v>-60.24812804653333</v>
+        <v>-61.69406826613334</v>
       </c>
       <c r="Q69">
-        <v>-60.04812804653334</v>
+        <v>-61.49406826613334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1113409511436775</v>
+        <v>0.1133891058669174</v>
       </c>
       <c r="T69">
-        <v>1.513647832417493</v>
+        <v>1.56094932718054</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07788923125083221</v>
+        <v>0.07674380137949642</v>
       </c>
       <c r="W69">
-        <v>0.2174337192710538</v>
+        <v>0.2177038116347148</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3781030643244282</v>
+        <v>0.3725427251431865</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7107,22 +7107,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1843231057890196</v>
+        <v>0.1862231057890196</v>
       </c>
       <c r="C70">
-        <v>-377.502876081364</v>
+        <v>-386.8292532276816</v>
       </c>
       <c r="D70">
-        <v>123.7611239186361</v>
+        <v>122.1577467723185</v>
       </c>
       <c r="E70">
-        <v>-74.03599999999994</v>
+        <v>-66.31299999999999</v>
       </c>
       <c r="F70">
-        <v>525.1640000000001</v>
+        <v>532.8870000000001</v>
       </c>
       <c r="G70">
         <v>23.9</v>
@@ -7143,37 +7143,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M70">
-        <v>123.8336712</v>
+        <v>125.6547546</v>
       </c>
       <c r="N70">
-        <v>-77.70033786666669</v>
+        <v>-79.52142126666668</v>
       </c>
       <c r="O70">
-        <v>-16.00626960053334</v>
+        <v>-16.38141278093334</v>
       </c>
       <c r="P70">
-        <v>-61.69406826613334</v>
+        <v>-63.14000848573334</v>
       </c>
       <c r="Q70">
-        <v>-61.49406826613334</v>
+        <v>-62.94000848573334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1133891058669174</v>
+        <v>0.1155693996045599</v>
       </c>
       <c r="T70">
-        <v>1.56094932718054</v>
+        <v>1.611302531283138</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07674380137949642</v>
+        <v>0.07563157237399648</v>
       </c>
       <c r="W70">
-        <v>0.2177038116347148</v>
+        <v>0.2179660752342117</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3725427251431865</v>
+        <v>0.3671435552135751</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7189,22 +7189,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1862231057890196</v>
+        <v>0.1881231057890196</v>
       </c>
       <c r="C71">
-        <v>-386.8292532276816</v>
+        <v>-396.1146168773317</v>
       </c>
       <c r="D71">
-        <v>122.1577467723185</v>
+        <v>120.5953831226685</v>
       </c>
       <c r="E71">
-        <v>-66.31299999999999</v>
+        <v>-58.58999999999992</v>
       </c>
       <c r="F71">
-        <v>532.8870000000001</v>
+        <v>540.6100000000001</v>
       </c>
       <c r="G71">
         <v>23.9</v>
@@ -7225,37 +7225,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M71">
-        <v>125.6547546</v>
+        <v>127.475838</v>
       </c>
       <c r="N71">
-        <v>-79.52142126666668</v>
+        <v>-81.3425046666667</v>
       </c>
       <c r="O71">
-        <v>-16.38141278093334</v>
+        <v>-16.75655596133334</v>
       </c>
       <c r="P71">
-        <v>-63.14000848573334</v>
+        <v>-64.58594870533335</v>
       </c>
       <c r="Q71">
-        <v>-62.94000848573334</v>
+        <v>-64.38594870533335</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1155693996045599</v>
+        <v>0.1178950462580452</v>
       </c>
       <c r="T71">
-        <v>1.611302531283138</v>
+        <v>1.665012615659242</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07563157237399648</v>
+        <v>0.07455112134008224</v>
       </c>
       <c r="W71">
-        <v>0.2179660752342117</v>
+        <v>0.2182208455880086</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3671435552135751</v>
+        <v>0.3618986472819525</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7271,22 +7271,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1881231057890196</v>
+        <v>0.1900231057890196</v>
       </c>
       <c r="C72">
-        <v>-396.1146168773317</v>
+        <v>-405.3605208115737</v>
       </c>
       <c r="D72">
-        <v>120.5953831226685</v>
+        <v>119.0724791884264</v>
       </c>
       <c r="E72">
-        <v>-58.58999999999992</v>
+        <v>-50.86699999999996</v>
       </c>
       <c r="F72">
-        <v>540.6100000000001</v>
+        <v>548.3330000000001</v>
       </c>
       <c r="G72">
         <v>23.9</v>
@@ -7307,37 +7307,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M72">
-        <v>127.475838</v>
+        <v>129.2969214</v>
       </c>
       <c r="N72">
-        <v>-81.3425046666667</v>
+        <v>-83.16358806666669</v>
       </c>
       <c r="O72">
-        <v>-16.75655596133334</v>
+        <v>-17.13169914173334</v>
       </c>
       <c r="P72">
-        <v>-64.58594870533335</v>
+        <v>-66.03188892493336</v>
       </c>
       <c r="Q72">
-        <v>-64.38594870533335</v>
+        <v>-65.83188892493335</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1178950462580452</v>
+        <v>0.1203810823359088</v>
       </c>
       <c r="T72">
-        <v>1.665012615659242</v>
+        <v>1.722426843785424</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07455112134008224</v>
+        <v>0.07350110554655996</v>
       </c>
       <c r="W72">
-        <v>0.2182208455880086</v>
+        <v>0.2184684393121212</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3618986472819525</v>
+        <v>0.3568014832357279</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7353,22 +7353,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1900231057890196</v>
+        <v>0.1919231057890196</v>
       </c>
       <c r="C73">
-        <v>-405.3605208115736</v>
+        <v>-414.568441304534</v>
       </c>
       <c r="D73">
-        <v>119.0724791884264</v>
+        <v>117.5875586954661</v>
       </c>
       <c r="E73">
-        <v>-50.86700000000008</v>
+        <v>-43.14400000000001</v>
       </c>
       <c r="F73">
-        <v>548.333</v>
+        <v>556.056</v>
       </c>
       <c r="G73">
         <v>23.9</v>
@@ -7389,37 +7389,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M73">
-        <v>129.2969214</v>
+        <v>131.1180048</v>
       </c>
       <c r="N73">
-        <v>-83.16358806666666</v>
+        <v>-84.98467146666668</v>
       </c>
       <c r="O73">
-        <v>-17.13169914173334</v>
+        <v>-17.50684232213334</v>
       </c>
       <c r="P73">
-        <v>-66.03188892493333</v>
+        <v>-67.47782914453335</v>
       </c>
       <c r="Q73">
-        <v>-65.83188892493332</v>
+        <v>-67.27782914453334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1203810823359088</v>
+        <v>0.1230446924193341</v>
       </c>
       <c r="T73">
-        <v>1.722426843785423</v>
+        <v>1.783942088206331</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07350110554655996</v>
+        <v>0.07248025685841329</v>
       </c>
       <c r="W73">
-        <v>0.2184684393121212</v>
+        <v>0.2187091554327862</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.356801483235728</v>
+        <v>0.3518459070796761</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7435,22 +7435,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1919231057890196</v>
+        <v>0.1938231057890196</v>
       </c>
       <c r="C74">
-        <v>-414.568441304534</v>
+        <v>-423.7397818965301</v>
       </c>
       <c r="D74">
-        <v>117.5875586954661</v>
+        <v>116.13921810347</v>
       </c>
       <c r="E74">
-        <v>-43.14400000000001</v>
+        <v>-35.42100000000005</v>
       </c>
       <c r="F74">
-        <v>556.056</v>
+        <v>563.779</v>
       </c>
       <c r="G74">
         <v>23.9</v>
@@ -7471,37 +7471,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M74">
-        <v>131.1180048</v>
+        <v>132.9390882</v>
       </c>
       <c r="N74">
-        <v>-84.98467146666668</v>
+        <v>-86.80575486666667</v>
       </c>
       <c r="O74">
-        <v>-17.50684232213334</v>
+        <v>-17.88198550253334</v>
       </c>
       <c r="P74">
-        <v>-67.47782914453335</v>
+        <v>-68.92376936413334</v>
       </c>
       <c r="Q74">
-        <v>-67.27782914453334</v>
+        <v>-68.72376936413333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1230446924193341</v>
+        <v>0.1259056069533835</v>
       </c>
       <c r="T74">
-        <v>1.783942088206331</v>
+        <v>1.850014017399158</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07248025685841329</v>
+        <v>0.07148737662747613</v>
       </c>
       <c r="W74">
-        <v>0.2187091554327862</v>
+        <v>0.2189432765912411</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3518459070796761</v>
+        <v>0.3470261001333792</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7517,22 +7517,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1938231057890196</v>
+        <v>0.1957231057890196</v>
       </c>
       <c r="C75">
-        <v>-423.7397818965301</v>
+        <v>-432.8758778189271</v>
       </c>
       <c r="D75">
-        <v>116.13921810347</v>
+        <v>114.726122181073</v>
       </c>
       <c r="E75">
-        <v>-35.42100000000005</v>
+        <v>-27.69799999999998</v>
       </c>
       <c r="F75">
-        <v>563.779</v>
+        <v>571.5020000000001</v>
       </c>
       <c r="G75">
         <v>23.9</v>
@@ -7553,37 +7553,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M75">
-        <v>132.9390882</v>
+        <v>134.7601716</v>
       </c>
       <c r="N75">
-        <v>-86.80575486666667</v>
+        <v>-88.6268382666667</v>
       </c>
       <c r="O75">
-        <v>-17.88198550253334</v>
+        <v>-18.25712868293334</v>
       </c>
       <c r="P75">
-        <v>-68.92376936413334</v>
+        <v>-70.36970958373335</v>
       </c>
       <c r="Q75">
-        <v>-68.72376936413333</v>
+        <v>-70.16970958373335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1259056069533835</v>
+        <v>0.128986591836206</v>
       </c>
       <c r="T75">
-        <v>1.850014017399158</v>
+        <v>1.921168402683741</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07148737662747613</v>
+        <v>0.07052133099737509</v>
       </c>
       <c r="W75">
-        <v>0.2189432765912411</v>
+        <v>0.219171070150819</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3470261001333792</v>
+        <v>0.3423365582396849</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7599,22 +7599,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1957231057890196</v>
+        <v>0.1976231057890196</v>
       </c>
       <c r="C76">
-        <v>-432.8758778189271</v>
+        <v>-441.9780000998444</v>
       </c>
       <c r="D76">
-        <v>114.726122181073</v>
+        <v>113.3469999001556</v>
       </c>
       <c r="E76">
-        <v>-27.69799999999998</v>
+        <v>-19.97500000000002</v>
       </c>
       <c r="F76">
-        <v>571.5020000000001</v>
+        <v>579.225</v>
       </c>
       <c r="G76">
         <v>23.9</v>
@@ -7635,37 +7635,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M76">
-        <v>134.7601716</v>
+        <v>136.581255</v>
       </c>
       <c r="N76">
-        <v>-88.6268382666667</v>
+        <v>-90.44792166666666</v>
       </c>
       <c r="O76">
-        <v>-18.25712868293334</v>
+        <v>-18.63227186333333</v>
       </c>
       <c r="P76">
-        <v>-70.36970958373335</v>
+        <v>-71.81564980333333</v>
       </c>
       <c r="Q76">
-        <v>-70.16970958373335</v>
+        <v>-71.61564980333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.128986591836206</v>
+        <v>0.1323140555096542</v>
       </c>
       <c r="T76">
-        <v>1.921168402683741</v>
+        <v>1.998015138791091</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07052133099737509</v>
+        <v>0.06958104658407678</v>
       </c>
       <c r="W76">
-        <v>0.219171070150819</v>
+        <v>0.2193927892154747</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3423365582396849</v>
+        <v>0.3377720707964892</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7681,22 +7681,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1976231057890196</v>
+        <v>0.1995231057890196</v>
       </c>
       <c r="C77">
-        <v>-441.9780000998444</v>
+        <v>-451.0473593772554</v>
       </c>
       <c r="D77">
-        <v>113.3469999001556</v>
+        <v>112.0006406227448</v>
       </c>
       <c r="E77">
-        <v>-19.97500000000002</v>
+        <v>-12.25199999999995</v>
       </c>
       <c r="F77">
-        <v>579.225</v>
+        <v>586.9480000000001</v>
       </c>
       <c r="G77">
         <v>23.9</v>
@@ -7717,37 +7717,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M77">
-        <v>136.581255</v>
+        <v>138.4023384</v>
       </c>
       <c r="N77">
-        <v>-90.44792166666666</v>
+        <v>-92.26900506666668</v>
       </c>
       <c r="O77">
-        <v>-18.63227186333333</v>
+        <v>-19.00741504373334</v>
       </c>
       <c r="P77">
-        <v>-71.81564980333333</v>
+        <v>-73.26159002293335</v>
       </c>
       <c r="Q77">
-        <v>-71.61564980333333</v>
+        <v>-73.06159002293334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1323140555096542</v>
+        <v>0.1359188078225565</v>
       </c>
       <c r="T77">
-        <v>1.998015138791091</v>
+        <v>2.081265769574053</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06958104658407678</v>
+        <v>0.06866550649744417</v>
       </c>
       <c r="W77">
-        <v>0.2193927892154747</v>
+        <v>0.2196086735679027</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3377720707964892</v>
+        <v>0.3333277014439038</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7763,22 +7763,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1995231057890196</v>
+        <v>0.2014231057890196</v>
       </c>
       <c r="C78">
-        <v>-451.0473593772554</v>
+        <v>-460.0851094435162</v>
       </c>
       <c r="D78">
-        <v>112.0006406227448</v>
+        <v>110.6858905564839</v>
       </c>
       <c r="E78">
-        <v>-12.25199999999995</v>
+        <v>-4.528999999999996</v>
       </c>
       <c r="F78">
-        <v>586.9480000000001</v>
+        <v>594.671</v>
       </c>
       <c r="G78">
         <v>23.9</v>
@@ -7799,37 +7799,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M78">
-        <v>138.4023384</v>
+        <v>140.2234218</v>
       </c>
       <c r="N78">
-        <v>-92.26900506666668</v>
+        <v>-94.09008846666667</v>
       </c>
       <c r="O78">
-        <v>-19.00741504373334</v>
+        <v>-19.38255822413334</v>
       </c>
       <c r="P78">
-        <v>-73.26159002293335</v>
+        <v>-74.70753024253334</v>
       </c>
       <c r="Q78">
-        <v>-73.06159002293334</v>
+        <v>-74.50753024253333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1359188078225565</v>
+        <v>0.1398370168583198</v>
       </c>
       <c r="T78">
-        <v>2.081265769574053</v>
+        <v>2.17175558564249</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06866550649744417</v>
+        <v>0.06777374667280205</v>
       </c>
       <c r="W78">
-        <v>0.2196086735679027</v>
+        <v>0.2198189505345533</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3333277014439038</v>
+        <v>0.3289987702563206</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7845,22 +7845,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2014231057890196</v>
+        <v>0.2033231057890196</v>
       </c>
       <c r="C79">
-        <v>-460.0851094435162</v>
+        <v>-469.0923505431448</v>
       </c>
       <c r="D79">
-        <v>110.6858905564839</v>
+        <v>109.4016494568553</v>
       </c>
       <c r="E79">
-        <v>-4.528999999999996</v>
+        <v>3.194000000000074</v>
       </c>
       <c r="F79">
-        <v>594.671</v>
+        <v>602.3940000000001</v>
       </c>
       <c r="G79">
         <v>23.9</v>
@@ -7881,37 +7881,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M79">
-        <v>140.2234218</v>
+        <v>142.0445052</v>
       </c>
       <c r="N79">
-        <v>-94.09008846666667</v>
+        <v>-95.91117186666669</v>
       </c>
       <c r="O79">
-        <v>-19.38255822413334</v>
+        <v>-19.75770140453334</v>
       </c>
       <c r="P79">
-        <v>-74.70753024253334</v>
+        <v>-76.15347046213336</v>
       </c>
       <c r="Q79">
-        <v>-74.50753024253333</v>
+        <v>-75.95347046213335</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1398370168583198</v>
+        <v>0.1441114267155162</v>
       </c>
       <c r="T79">
-        <v>2.17175558564249</v>
+        <v>2.27047174862624</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06777374667280205</v>
+        <v>0.06690485248468919</v>
       </c>
       <c r="W79">
-        <v>0.2198189505345533</v>
+        <v>0.2200238357841103</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3289987702563206</v>
+        <v>0.3247808373043164</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7927,22 +7927,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2033231057890196</v>
+        <v>0.2052231057890196</v>
       </c>
       <c r="C80">
-        <v>-469.0923505431448</v>
+        <v>-478.0701324436533</v>
       </c>
       <c r="D80">
-        <v>109.4016494568553</v>
+        <v>108.1468675563468</v>
       </c>
       <c r="E80">
-        <v>3.194000000000074</v>
+        <v>10.91700000000003</v>
       </c>
       <c r="F80">
-        <v>602.3940000000001</v>
+        <v>610.1170000000001</v>
       </c>
       <c r="G80">
         <v>23.9</v>
@@ -7963,37 +7963,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M80">
-        <v>142.0445052</v>
+        <v>143.8655886</v>
       </c>
       <c r="N80">
-        <v>-95.91117186666669</v>
+        <v>-97.73225526666668</v>
       </c>
       <c r="O80">
-        <v>-19.75770140453334</v>
+        <v>-20.13284458493334</v>
       </c>
       <c r="P80">
-        <v>-76.15347046213336</v>
+        <v>-77.59941068173335</v>
       </c>
       <c r="Q80">
-        <v>-75.95347046213335</v>
+        <v>-77.39941068173334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1441114267155162</v>
+        <v>0.1487929232257789</v>
       </c>
       <c r="T80">
-        <v>2.27047174862624</v>
+        <v>2.378589450941775</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06690485248468919</v>
+        <v>0.06605795561779439</v>
       </c>
       <c r="W80">
-        <v>0.2200238357841103</v>
+        <v>0.2202235340653241</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3247808373043164</v>
+        <v>0.3206696874650213</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8009,22 +8009,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2052231057890196</v>
+        <v>0.2071231057890196</v>
       </c>
       <c r="C81">
-        <v>-478.0701324436533</v>
+        <v>-487.0194572974537</v>
       </c>
       <c r="D81">
-        <v>108.1468675563468</v>
+        <v>106.9205427025465</v>
       </c>
       <c r="E81">
-        <v>10.91700000000003</v>
+        <v>18.6400000000001</v>
       </c>
       <c r="F81">
-        <v>610.1170000000001</v>
+        <v>617.8400000000001</v>
       </c>
       <c r="G81">
         <v>23.9</v>
@@ -8045,37 +8045,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M81">
-        <v>143.8655886</v>
+        <v>145.686672</v>
       </c>
       <c r="N81">
-        <v>-97.73225526666668</v>
+        <v>-99.5533386666667</v>
       </c>
       <c r="O81">
-        <v>-20.13284458493334</v>
+        <v>-20.50798776533334</v>
       </c>
       <c r="P81">
-        <v>-77.59941068173335</v>
+        <v>-79.04535090133336</v>
       </c>
       <c r="Q81">
-        <v>-77.39941068173334</v>
+        <v>-78.84535090133336</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1487929232257789</v>
+        <v>0.1539425693870678</v>
       </c>
       <c r="T81">
-        <v>2.378589450941775</v>
+        <v>2.497518923488864</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06605795561779439</v>
+        <v>0.06523223117257196</v>
       </c>
       <c r="W81">
-        <v>0.2202235340653241</v>
+        <v>0.2204182398895075</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3206696874650213</v>
+        <v>0.3166613163717085</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8091,22 +8091,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2071231057890196</v>
+        <v>0.2090231057890196</v>
       </c>
       <c r="C82">
-        <v>-487.0194572974537</v>
+        <v>-495.941282311231</v>
       </c>
       <c r="D82">
-        <v>106.9205427025465</v>
+        <v>105.7217176887691</v>
       </c>
       <c r="E82">
-        <v>18.6400000000001</v>
+        <v>26.36300000000006</v>
       </c>
       <c r="F82">
-        <v>617.8400000000001</v>
+        <v>625.5630000000001</v>
       </c>
       <c r="G82">
         <v>23.9</v>
@@ -8127,37 +8127,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M82">
-        <v>145.686672</v>
+        <v>147.5077554</v>
       </c>
       <c r="N82">
-        <v>-99.5533386666667</v>
+        <v>-101.3744220666667</v>
       </c>
       <c r="O82">
-        <v>-20.50798776533334</v>
+        <v>-20.88313094573334</v>
       </c>
       <c r="P82">
-        <v>-79.04535090133336</v>
+        <v>-80.49129112093335</v>
       </c>
       <c r="Q82">
-        <v>-78.84535090133336</v>
+        <v>-80.29129112093335</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1539425693870678</v>
+        <v>0.1596342835653345</v>
       </c>
       <c r="T82">
-        <v>2.497518923488864</v>
+        <v>2.628967287883015</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06523223117257196</v>
+        <v>0.06442689498525625</v>
       </c>
       <c r="W82">
-        <v>0.2204182398895075</v>
+        <v>0.2206081381624766</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3166613163717085</v>
+        <v>0.3127519174041565</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8173,22 +8173,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2090231057890196</v>
+        <v>0.2109231057890196</v>
       </c>
       <c r="C83">
-        <v>-495.941282311231</v>
+        <v>-504.836522237729</v>
       </c>
       <c r="D83">
-        <v>105.7217176887691</v>
+        <v>104.5494777622711</v>
       </c>
       <c r="E83">
-        <v>26.36300000000006</v>
+        <v>34.08600000000001</v>
       </c>
       <c r="F83">
-        <v>625.5630000000001</v>
+        <v>633.2860000000001</v>
       </c>
       <c r="G83">
         <v>23.9</v>
@@ -8209,37 +8209,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M83">
-        <v>147.5077554</v>
+        <v>149.3288388</v>
       </c>
       <c r="N83">
-        <v>-101.3744220666667</v>
+        <v>-103.1955054666667</v>
       </c>
       <c r="O83">
-        <v>-20.88313094573334</v>
+        <v>-21.25827412613334</v>
       </c>
       <c r="P83">
-        <v>-80.49129112093335</v>
+        <v>-81.93723134053334</v>
       </c>
       <c r="Q83">
-        <v>-80.29129112093335</v>
+        <v>-81.73723134053334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1596342835653345</v>
+        <v>0.1659584104300753</v>
       </c>
       <c r="T83">
-        <v>2.628967287883015</v>
+        <v>2.775021026098738</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06442689498525625</v>
+        <v>0.06364120114397265</v>
       </c>
       <c r="W83">
-        <v>0.2206081381624766</v>
+        <v>0.2207934047702513</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3127519174041565</v>
+        <v>0.3089378696309352</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8255,22 +8255,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2109231057890196</v>
+        <v>0.2128231057890196</v>
       </c>
       <c r="C84">
-        <v>-504.836522237729</v>
+        <v>-513.7060517035811</v>
       </c>
       <c r="D84">
-        <v>104.5494777622711</v>
+        <v>103.402948296419</v>
       </c>
       <c r="E84">
-        <v>34.08600000000001</v>
+        <v>41.80900000000008</v>
       </c>
       <c r="F84">
-        <v>633.2860000000001</v>
+        <v>641.0090000000001</v>
       </c>
       <c r="G84">
         <v>23.9</v>
@@ -8291,37 +8291,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M84">
-        <v>149.3288388</v>
+        <v>151.1499222</v>
       </c>
       <c r="N84">
-        <v>-103.1955054666667</v>
+        <v>-105.0165888666667</v>
       </c>
       <c r="O84">
-        <v>-21.25827412613334</v>
+        <v>-21.63341730653334</v>
       </c>
       <c r="P84">
-        <v>-81.93723134053334</v>
+        <v>-83.38317156013336</v>
       </c>
       <c r="Q84">
-        <v>-81.73723134053334</v>
+        <v>-83.18317156013336</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1659584104300753</v>
+        <v>0.1730265522200798</v>
       </c>
       <c r="T84">
-        <v>2.775021026098738</v>
+        <v>2.938257557045723</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06364120114397265</v>
+        <v>0.0628744396844067</v>
       </c>
       <c r="W84">
-        <v>0.2207934047702513</v>
+        <v>0.2209742071224169</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3089378696309352</v>
+        <v>0.3052157266233335</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8337,22 +8337,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2128231057890196</v>
+        <v>0.2147231057890196</v>
       </c>
       <c r="C85">
-        <v>-513.7060517035811</v>
+        <v>-522.550707385635</v>
       </c>
       <c r="D85">
-        <v>103.402948296419</v>
+        <v>102.2812926143651</v>
       </c>
       <c r="E85">
-        <v>41.80900000000008</v>
+        <v>49.53200000000004</v>
       </c>
       <c r="F85">
-        <v>641.0090000000001</v>
+        <v>648.7320000000001</v>
       </c>
       <c r="G85">
         <v>23.9</v>
@@ -8373,37 +8373,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M85">
-        <v>151.1499222</v>
+        <v>152.9710056</v>
       </c>
       <c r="N85">
-        <v>-105.0165888666667</v>
+        <v>-106.8376722666667</v>
       </c>
       <c r="O85">
-        <v>-21.63341730653334</v>
+        <v>-22.00856048693334</v>
       </c>
       <c r="P85">
-        <v>-83.38317156013336</v>
+        <v>-84.82911177973334</v>
       </c>
       <c r="Q85">
-        <v>-83.18317156013336</v>
+        <v>-84.62911177973334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1730265522200798</v>
+        <v>0.1809782117338348</v>
       </c>
       <c r="T85">
-        <v>2.938257557045723</v>
+        <v>3.121898654361081</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0628744396844067</v>
+        <v>0.06212593445006855</v>
       </c>
       <c r="W85">
-        <v>0.2209742071224169</v>
+        <v>0.2211507046566739</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3052157266233335</v>
+        <v>0.3015822060682939</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8419,22 +8419,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2147231057890196</v>
+        <v>0.2166231057890196</v>
       </c>
       <c r="C86">
-        <v>-522.550707385635</v>
+        <v>-531.371290047152</v>
       </c>
       <c r="D86">
-        <v>102.2812926143652</v>
+        <v>101.183709952848</v>
       </c>
       <c r="E86">
-        <v>49.53200000000004</v>
+        <v>57.255</v>
       </c>
       <c r="F86">
-        <v>648.7320000000001</v>
+        <v>656.455</v>
       </c>
       <c r="G86">
         <v>23.9</v>
@@ -8455,37 +8455,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M86">
-        <v>152.9710056</v>
+        <v>154.792089</v>
       </c>
       <c r="N86">
-        <v>-106.8376722666667</v>
+        <v>-108.6587556666667</v>
       </c>
       <c r="O86">
-        <v>-22.00856048693334</v>
+        <v>-22.38370366733334</v>
       </c>
       <c r="P86">
-        <v>-84.82911177973334</v>
+        <v>-86.27505199933333</v>
       </c>
       <c r="Q86">
-        <v>-84.62911177973334</v>
+        <v>-86.07505199933333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1809782117338347</v>
+        <v>0.1899900925160903</v>
       </c>
       <c r="T86">
-        <v>3.121898654361079</v>
+        <v>3.330025231318484</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06212593445006855</v>
+        <v>0.06139504110359715</v>
       </c>
       <c r="W86">
-        <v>0.2211507046566739</v>
+        <v>0.2213230493077718</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3015822060682939</v>
+        <v>0.2980341801145493</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8501,22 +8501,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2166231057890196</v>
+        <v>0.2185231057890196</v>
       </c>
       <c r="C87">
-        <v>-531.371290047152</v>
+        <v>-540.1685664442964</v>
       </c>
       <c r="D87">
-        <v>101.183709952848</v>
+        <v>100.1094335557036</v>
       </c>
       <c r="E87">
-        <v>57.255</v>
+        <v>64.97799999999995</v>
       </c>
       <c r="F87">
-        <v>656.455</v>
+        <v>664.178</v>
       </c>
       <c r="G87">
         <v>23.9</v>
@@ -8537,37 +8537,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M87">
-        <v>154.792089</v>
+        <v>156.6131724</v>
       </c>
       <c r="N87">
-        <v>-108.6587556666667</v>
+        <v>-110.4798390666667</v>
       </c>
       <c r="O87">
-        <v>-22.38370366733334</v>
+        <v>-22.75884684773333</v>
       </c>
       <c r="P87">
-        <v>-86.27505199933333</v>
+        <v>-87.72099221893332</v>
       </c>
       <c r="Q87">
-        <v>-86.07505199933333</v>
+        <v>-87.52099221893332</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1899900925160903</v>
+        <v>0.2002893848386682</v>
       </c>
       <c r="T87">
-        <v>3.330025231318484</v>
+        <v>3.567884176412662</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06139504110359715</v>
+        <v>0.06068114527681114</v>
       </c>
       <c r="W87">
-        <v>0.2213230493077718</v>
+        <v>0.2214913859437279</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2980341801145493</v>
+        <v>0.2945686663922871</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8583,22 +8583,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2185231057890196</v>
+        <v>0.2204231057890196</v>
       </c>
       <c r="C88">
-        <v>-540.1685664442964</v>
+        <v>-548.9432711124514</v>
       </c>
       <c r="D88">
-        <v>100.1094335557036</v>
+        <v>99.05772888754873</v>
       </c>
       <c r="E88">
-        <v>64.97799999999995</v>
+        <v>72.70100000000002</v>
       </c>
       <c r="F88">
-        <v>664.178</v>
+        <v>671.9010000000001</v>
       </c>
       <c r="G88">
         <v>23.9</v>
@@ -8619,37 +8619,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M88">
-        <v>156.6131724</v>
+        <v>158.4342558</v>
       </c>
       <c r="N88">
-        <v>-110.4798390666667</v>
+        <v>-112.3009224666667</v>
       </c>
       <c r="O88">
-        <v>-22.75884684773333</v>
+        <v>-23.13399002813334</v>
       </c>
       <c r="P88">
-        <v>-87.72099221893332</v>
+        <v>-89.16693243853334</v>
       </c>
       <c r="Q88">
-        <v>-87.52099221893332</v>
+        <v>-88.96693243853333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2002893848386682</v>
+        <v>0.2121731836724119</v>
       </c>
       <c r="T88">
-        <v>3.567884176412662</v>
+        <v>3.842336805367482</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06068114527681114</v>
+        <v>0.05998366084834204</v>
       </c>
       <c r="W88">
-        <v>0.2214913859437279</v>
+        <v>0.221655852771961</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2945686663922871</v>
+        <v>0.2911828196521458</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8665,22 +8665,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2204231057890196</v>
+        <v>0.2223231057890196</v>
       </c>
       <c r="C89">
-        <v>-548.9432711124514</v>
+        <v>-557.6961080411077</v>
       </c>
       <c r="D89">
-        <v>99.05772888754873</v>
+        <v>98.02789195889235</v>
       </c>
       <c r="E89">
-        <v>72.70100000000002</v>
+        <v>80.42399999999998</v>
       </c>
       <c r="F89">
-        <v>671.9010000000001</v>
+        <v>679.624</v>
       </c>
       <c r="G89">
         <v>23.9</v>
@@ -8701,37 +8701,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M89">
-        <v>158.4342558</v>
+        <v>160.2553392</v>
       </c>
       <c r="N89">
-        <v>-112.3009224666667</v>
+        <v>-114.1220058666667</v>
       </c>
       <c r="O89">
-        <v>-23.13399002813334</v>
+        <v>-23.50913320853333</v>
       </c>
       <c r="P89">
-        <v>-89.16693243853334</v>
+        <v>-90.61287265813334</v>
       </c>
       <c r="Q89">
-        <v>-88.96693243853333</v>
+        <v>-90.41287265813334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2121731836724119</v>
+        <v>0.226037615645113</v>
       </c>
       <c r="T89">
-        <v>3.842336805367482</v>
+        <v>4.162531539148106</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05998366084834204</v>
+        <v>0.0593020283387018</v>
       </c>
       <c r="W89">
-        <v>0.221655852771961</v>
+        <v>0.2218165817177341</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2911828196521458</v>
+        <v>0.2878739239742806</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8747,22 +8747,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2223231057890196</v>
+        <v>0.2242231057890196</v>
       </c>
       <c r="C90">
-        <v>-557.6961080411077</v>
+        <v>-566.4277522453538</v>
       </c>
       <c r="D90">
-        <v>98.02789195889235</v>
+        <v>97.01924775464629</v>
       </c>
       <c r="E90">
-        <v>80.42399999999998</v>
+        <v>88.14700000000005</v>
       </c>
       <c r="F90">
-        <v>679.624</v>
+        <v>687.3470000000001</v>
       </c>
       <c r="G90">
         <v>23.9</v>
@@ -8783,37 +8783,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M90">
-        <v>160.2553392</v>
+        <v>162.0764226</v>
       </c>
       <c r="N90">
-        <v>-114.1220058666667</v>
+        <v>-115.9430892666667</v>
       </c>
       <c r="O90">
-        <v>-23.50913320853333</v>
+        <v>-23.88427638893334</v>
       </c>
       <c r="P90">
-        <v>-90.61287265813334</v>
+        <v>-92.05881287773335</v>
       </c>
       <c r="Q90">
-        <v>-90.41287265813334</v>
+        <v>-91.85881287773334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.226037615645113</v>
+        <v>0.2424228534310323</v>
       </c>
       <c r="T90">
-        <v>4.162531539148106</v>
+        <v>4.54094349725248</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0593020283387018</v>
+        <v>0.05863571341354783</v>
       </c>
       <c r="W90">
-        <v>0.2218165817177341</v>
+        <v>0.2219736987770854</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2878739239742806</v>
+        <v>0.2846393855026593</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8829,22 +8829,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2242231057890196</v>
+        <v>0.2261231057890196</v>
       </c>
       <c r="C91">
-        <v>-566.4277522453538</v>
+        <v>-575.1388512413328</v>
       </c>
       <c r="D91">
-        <v>97.01924775464629</v>
+        <v>96.03114875866727</v>
       </c>
       <c r="E91">
-        <v>88.14700000000005</v>
+        <v>95.87</v>
       </c>
       <c r="F91">
-        <v>687.3470000000001</v>
+        <v>695.0700000000001</v>
       </c>
       <c r="G91">
         <v>23.9</v>
@@ -8865,37 +8865,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M91">
-        <v>162.0764226</v>
+        <v>163.897506</v>
       </c>
       <c r="N91">
-        <v>-115.9430892666667</v>
+        <v>-117.7641726666667</v>
       </c>
       <c r="O91">
-        <v>-23.88427638893334</v>
+        <v>-24.25941956933334</v>
       </c>
       <c r="P91">
-        <v>-92.05881287773335</v>
+        <v>-93.50475309733335</v>
       </c>
       <c r="Q91">
-        <v>-91.85881287773334</v>
+        <v>-93.30475309733335</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2424228534310323</v>
+        <v>0.2620851387741356</v>
       </c>
       <c r="T91">
-        <v>4.54094349725248</v>
+        <v>4.995037846977728</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05863571341354783</v>
+        <v>0.05798420548673064</v>
       </c>
       <c r="W91">
-        <v>0.2219736987770854</v>
+        <v>0.2221273243462289</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2846393855026593</v>
+        <v>0.2814767256637409</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8911,22 +8911,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2261231057890196</v>
+        <v>0.2280231057890196</v>
       </c>
       <c r="C92">
-        <v>-575.1388512413328</v>
+        <v>-583.8300264324498</v>
       </c>
       <c r="D92">
-        <v>96.03114875866727</v>
+        <v>95.06297356755037</v>
       </c>
       <c r="E92">
-        <v>95.87</v>
+        <v>103.5930000000001</v>
       </c>
       <c r="F92">
-        <v>695.0700000000001</v>
+        <v>702.7930000000001</v>
       </c>
       <c r="G92">
         <v>23.9</v>
@@ -8947,37 +8947,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M92">
-        <v>163.897506</v>
+        <v>165.7185894</v>
       </c>
       <c r="N92">
-        <v>-117.7641726666667</v>
+        <v>-119.5852560666667</v>
       </c>
       <c r="O92">
-        <v>-24.25941956933334</v>
+        <v>-24.63456274973334</v>
       </c>
       <c r="P92">
-        <v>-93.50475309733335</v>
+        <v>-94.95069331693335</v>
       </c>
       <c r="Q92">
-        <v>-93.30475309733335</v>
+        <v>-94.75069331693335</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2620851387741356</v>
+        <v>0.2861168208601507</v>
       </c>
       <c r="T92">
-        <v>4.995037846977728</v>
+        <v>5.550042052197476</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05798420548673064</v>
+        <v>0.05734701641544788</v>
       </c>
       <c r="W92">
-        <v>0.2221273243462289</v>
+        <v>0.2222775735292374</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2814767256637409</v>
+        <v>0.2783835748322713</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8993,22 +8993,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2280231057890196</v>
+        <v>0.2299231057890196</v>
       </c>
       <c r="C93">
-        <v>-583.8300264324498</v>
+        <v>-592.5018744125609</v>
       </c>
       <c r="D93">
-        <v>95.06297356755037</v>
+        <v>94.11412558743916</v>
       </c>
       <c r="E93">
-        <v>103.5930000000001</v>
+        <v>111.316</v>
       </c>
       <c r="F93">
-        <v>702.7930000000001</v>
+        <v>710.5160000000001</v>
       </c>
       <c r="G93">
         <v>23.9</v>
@@ -9029,37 +9029,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M93">
-        <v>165.7185894</v>
+        <v>167.5396728</v>
       </c>
       <c r="N93">
-        <v>-119.5852560666667</v>
+        <v>-121.4063394666667</v>
       </c>
       <c r="O93">
-        <v>-24.63456274973334</v>
+        <v>-25.00970593013334</v>
       </c>
       <c r="P93">
-        <v>-94.95069331693335</v>
+        <v>-96.39663353653336</v>
       </c>
       <c r="Q93">
-        <v>-94.75069331693335</v>
+        <v>-96.19663353653335</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2861168208601507</v>
+        <v>0.3161564234676695</v>
       </c>
       <c r="T93">
-        <v>5.550042052197476</v>
+        <v>6.243797308722161</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05734701641544788</v>
+        <v>0.05672367928049736</v>
       </c>
       <c r="W93">
-        <v>0.2222775735292374</v>
+        <v>0.2224245564256587</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2783835748322713</v>
+        <v>0.2753576664101813</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9075,22 +9075,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2299231057890196</v>
+        <v>0.2318231057890196</v>
       </c>
       <c r="C94">
-        <v>-592.5018744125609</v>
+        <v>-601.1549681918905</v>
       </c>
       <c r="D94">
-        <v>94.11412558743916</v>
+        <v>93.18403180810967</v>
       </c>
       <c r="E94">
-        <v>111.316</v>
+        <v>119.0390000000001</v>
       </c>
       <c r="F94">
-        <v>710.5160000000001</v>
+        <v>718.2390000000001</v>
       </c>
       <c r="G94">
         <v>23.9</v>
@@ -9111,37 +9111,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M94">
-        <v>167.5396728</v>
+        <v>169.3607562000001</v>
       </c>
       <c r="N94">
-        <v>-121.4063394666667</v>
+        <v>-123.2274228666667</v>
       </c>
       <c r="O94">
-        <v>-25.00970593013334</v>
+        <v>-25.38484911053335</v>
       </c>
       <c r="P94">
-        <v>-96.39663353653336</v>
+        <v>-97.84257375613336</v>
       </c>
       <c r="Q94">
-        <v>-96.19663353653335</v>
+        <v>-97.64257375613336</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3161564234676695</v>
+        <v>0.3547787696773367</v>
       </c>
       <c r="T94">
-        <v>6.243797308722161</v>
+        <v>7.135768352825329</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05672367928049736</v>
+        <v>0.05611374724522319</v>
       </c>
       <c r="W94">
-        <v>0.2224245564256587</v>
+        <v>0.2225683783995764</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2753576664101813</v>
+        <v>0.2723968312874911</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9157,22 +9157,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2318231057890196</v>
+        <v>0.2337231057890196</v>
       </c>
       <c r="C95">
-        <v>-601.1549681918905</v>
+        <v>-609.7898583509659</v>
       </c>
       <c r="D95">
-        <v>93.18403180810967</v>
+        <v>92.2721416490342</v>
       </c>
       <c r="E95">
-        <v>119.0390000000001</v>
+        <v>126.7620000000001</v>
       </c>
       <c r="F95">
-        <v>718.2390000000001</v>
+        <v>725.9620000000001</v>
       </c>
       <c r="G95">
         <v>23.9</v>
@@ -9193,37 +9193,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M95">
-        <v>169.3607562000001</v>
+        <v>171.1818396</v>
       </c>
       <c r="N95">
-        <v>-123.2274228666667</v>
+        <v>-125.0485062666667</v>
       </c>
       <c r="O95">
-        <v>-25.38484911053335</v>
+        <v>-25.75999229093334</v>
       </c>
       <c r="P95">
-        <v>-97.84257375613336</v>
+        <v>-99.28851397573334</v>
       </c>
       <c r="Q95">
-        <v>-97.64257375613336</v>
+        <v>-99.08851397573333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3547787696773367</v>
+        <v>0.4062752312902262</v>
       </c>
       <c r="T95">
-        <v>7.135768352825329</v>
+        <v>8.325063078296219</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05611374724522319</v>
+        <v>0.05551679248729529</v>
       </c>
       <c r="W95">
-        <v>0.2225683783995764</v>
+        <v>0.2227091403314958</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2723968312874911</v>
+        <v>0.2694989926567732</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9239,22 +9239,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2337231057890196</v>
+        <v>0.2356231057890196</v>
       </c>
       <c r="C96">
-        <v>-609.7898583509659</v>
+        <v>-618.4070741274575</v>
       </c>
       <c r="D96">
-        <v>92.2721416490342</v>
+        <v>91.37792587254269</v>
       </c>
       <c r="E96">
-        <v>126.7620000000001</v>
+        <v>134.4850000000001</v>
       </c>
       <c r="F96">
-        <v>725.9620000000001</v>
+        <v>733.6850000000002</v>
       </c>
       <c r="G96">
         <v>23.9</v>
@@ -9275,37 +9275,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M96">
-        <v>171.1818396</v>
+        <v>173.002923</v>
       </c>
       <c r="N96">
-        <v>-125.0485062666667</v>
+        <v>-126.8695896666667</v>
       </c>
       <c r="O96">
-        <v>-25.75999229093334</v>
+        <v>-26.13513547133334</v>
       </c>
       <c r="P96">
-        <v>-99.28851397573334</v>
+        <v>-100.7344541953334</v>
       </c>
       <c r="Q96">
-        <v>-99.08851397573333</v>
+        <v>-100.5344541953334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4062752312902262</v>
+        <v>0.4783702775482716</v>
       </c>
       <c r="T96">
-        <v>8.325063078296219</v>
+        <v>9.990075693955466</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05551679248729529</v>
+        <v>0.05493240519795534</v>
       </c>
       <c r="W96">
-        <v>0.2227091403314958</v>
+        <v>0.2228469388543221</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2694989926567732</v>
+        <v>0.266662161155123</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9321,22 +9321,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2356231057890196</v>
+        <v>0.2375231057890196</v>
       </c>
       <c r="C97">
-        <v>-618.4070741274575</v>
+        <v>-627.0071244404271</v>
       </c>
       <c r="D97">
-        <v>91.37792587254269</v>
+        <v>90.500875559573</v>
       </c>
       <c r="E97">
-        <v>134.4850000000001</v>
+        <v>142.2080000000001</v>
       </c>
       <c r="F97">
-        <v>733.6850000000002</v>
+        <v>741.4080000000001</v>
       </c>
       <c r="G97">
         <v>23.9</v>
@@ -9357,37 +9357,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M97">
-        <v>173.002923</v>
+        <v>174.8240064</v>
       </c>
       <c r="N97">
-        <v>-126.8695896666667</v>
+        <v>-128.6906730666667</v>
       </c>
       <c r="O97">
-        <v>-26.13513547133334</v>
+        <v>-26.51027865173334</v>
       </c>
       <c r="P97">
-        <v>-100.7344541953334</v>
+        <v>-102.1803944149334</v>
       </c>
       <c r="Q97">
-        <v>-100.5344541953334</v>
+        <v>-101.9803944149334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4783702775482716</v>
+        <v>0.5865128469353398</v>
       </c>
       <c r="T97">
-        <v>9.990075693955466</v>
+        <v>12.48759461744434</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05493240519795534</v>
+        <v>0.05436019264380997</v>
       </c>
       <c r="W97">
-        <v>0.2228469388543221</v>
+        <v>0.2229818665745896</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.266662161155123</v>
+        <v>0.2638844303097571</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9403,22 +9403,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2375231057890196</v>
+        <v>0.2394231057890196</v>
       </c>
       <c r="C98">
-        <v>-627.007124440427</v>
+        <v>-635.5904988561545</v>
       </c>
       <c r="D98">
-        <v>90.500875559573</v>
+        <v>89.64050114384565</v>
       </c>
       <c r="E98">
-        <v>142.208</v>
+        <v>149.931</v>
       </c>
       <c r="F98">
-        <v>741.408</v>
+        <v>749.1310000000001</v>
       </c>
       <c r="G98">
         <v>23.9</v>
@@ -9439,37 +9439,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M98">
-        <v>174.8240064</v>
+        <v>176.6450898</v>
       </c>
       <c r="N98">
-        <v>-128.6906730666666</v>
+        <v>-130.5117564666667</v>
       </c>
       <c r="O98">
-        <v>-26.51027865173333</v>
+        <v>-26.88542183213334</v>
       </c>
       <c r="P98">
-        <v>-102.1803944149333</v>
+        <v>-103.6263346345333</v>
       </c>
       <c r="Q98">
-        <v>-101.9803944149333</v>
+        <v>-103.4263346345333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5865128469353383</v>
+        <v>0.7667504625804512</v>
       </c>
       <c r="T98">
-        <v>12.48759461744431</v>
+        <v>16.65012615659241</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05436019264380998</v>
+        <v>0.05379977828665729</v>
       </c>
       <c r="W98">
-        <v>0.2229818665745896</v>
+        <v>0.2231140122800062</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2638844303097573</v>
+        <v>0.2611639722653267</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9485,22 +9485,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2394231057890196</v>
+        <v>0.2413231057890196</v>
       </c>
       <c r="C99">
-        <v>-635.5904988561545</v>
+        <v>-644.1576684993893</v>
       </c>
       <c r="D99">
-        <v>89.64050114384565</v>
+        <v>88.7963315006108</v>
       </c>
       <c r="E99">
-        <v>149.931</v>
+        <v>157.654</v>
       </c>
       <c r="F99">
-        <v>749.1310000000001</v>
+        <v>756.854</v>
       </c>
       <c r="G99">
         <v>23.9</v>
@@ -9521,37 +9521,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M99">
-        <v>176.6450898</v>
+        <v>178.4661732</v>
       </c>
       <c r="N99">
-        <v>-130.5117564666667</v>
+        <v>-132.3328398666667</v>
       </c>
       <c r="O99">
-        <v>-26.88542183213334</v>
+        <v>-27.26056501253334</v>
       </c>
       <c r="P99">
-        <v>-103.6263346345333</v>
+        <v>-105.0722748541334</v>
       </c>
       <c r="Q99">
-        <v>-103.4263346345333</v>
+        <v>-104.8722748541334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7667504625804512</v>
+        <v>1.127225693870677</v>
       </c>
       <c r="T99">
-        <v>16.65012615659241</v>
+        <v>24.97518923488861</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05379977828665729</v>
+        <v>0.0532508009572016</v>
       </c>
       <c r="W99">
-        <v>0.2231140122800062</v>
+        <v>0.2232434611342919</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2611639722653267</v>
+        <v>0.2584990337728232</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9567,22 +9567,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2413231057890196</v>
+        <v>0.2432231057890196</v>
       </c>
       <c r="C100">
-        <v>-644.1576684993893</v>
+        <v>-652.7090869135959</v>
       </c>
       <c r="D100">
-        <v>88.7963315006108</v>
+        <v>87.96791308640417</v>
       </c>
       <c r="E100">
-        <v>157.654</v>
+        <v>165.3770000000001</v>
       </c>
       <c r="F100">
-        <v>756.854</v>
+        <v>764.5770000000001</v>
       </c>
       <c r="G100">
         <v>23.9</v>
@@ -9603,37 +9603,37 @@
         <v>46.13333333333334</v>
       </c>
       <c r="M100">
-        <v>178.4661732</v>
+        <v>180.2872566</v>
       </c>
       <c r="N100">
-        <v>-132.3328398666667</v>
+        <v>-134.1539232666667</v>
       </c>
       <c r="O100">
-        <v>-27.26056501253334</v>
+        <v>-27.63570819293334</v>
       </c>
       <c r="P100">
-        <v>-105.0722748541334</v>
+        <v>-106.5182150737334</v>
       </c>
       <c r="Q100">
-        <v>-104.8722748541334</v>
+        <v>-106.3182150737334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.127225693870677</v>
+        <v>2.208651387741353</v>
       </c>
       <c r="T100">
-        <v>24.97518923488861</v>
+        <v>49.95037846977723</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0532508009572016</v>
+        <v>0.05271291407884603</v>
       </c>
       <c r="W100">
-        <v>0.2232434611342919</v>
+        <v>0.2233702948602081</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9641,91 +9641,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2584990337728232</v>
+        <v>0.2558879324215826</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2432231057890196</v>
-      </c>
-      <c r="C101">
-        <v>-652.7090869135959</v>
-      </c>
-      <c r="D101">
-        <v>87.96791308640417</v>
-      </c>
-      <c r="E101">
-        <v>165.3770000000001</v>
-      </c>
-      <c r="F101">
-        <v>764.5770000000001</v>
-      </c>
-      <c r="G101">
-        <v>23.9</v>
-      </c>
-      <c r="H101">
-        <v>173.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>46.33333333333334</v>
-      </c>
-      <c r="K101">
-        <v>0.1999999999999993</v>
-      </c>
-      <c r="L101">
-        <v>46.13333333333334</v>
-      </c>
-      <c r="M101">
-        <v>180.2872566</v>
-      </c>
-      <c r="N101">
-        <v>-134.1539232666667</v>
-      </c>
-      <c r="O101">
-        <v>-27.63570819293334</v>
-      </c>
-      <c r="P101">
-        <v>-106.5182150737334</v>
-      </c>
-      <c r="Q101">
-        <v>-106.3182150737334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.208651387741353</v>
-      </c>
-      <c r="T101">
-        <v>49.95037846977723</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05271291407884603</v>
-      </c>
-      <c r="W101">
-        <v>0.2233702948602081</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2558879324215826</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
